--- a/outputs/samc21-pin-allocation/samc21_pin_allocation.xlsx
+++ b/outputs/samc21-pin-allocation/samc21_pin_allocation.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R2ccacb07d0b34804"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAM0" sheetId="2" r:id="R5966797324fb4981"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAM1" sheetId="3" r:id="R7a3e89122b3c4995"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAM2" sheetId="4" r:id="R2346af05269043c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STM32" sheetId="5" r:id="Reddc905ecbe44354"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FTDI" sheetId="6" r:id="R4504b132092c4a49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R7203cc0b85584988"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAM0" sheetId="2" r:id="R6f9f200a0a5a4d68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAM1" sheetId="3" r:id="R2efb696a4a57481a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAM2" sheetId="4" r:id="R6c8137ec712c4a86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STM32" sheetId="5" r:id="R037ca390c10d46fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FTDI" sheetId="6" r:id="R11c7b9a793ea4e7e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -477,14 +477,14 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="5" t="str">
-        <x:v>SAMC21 draft pin allocation</x:v>
+        <x:v>Board 1 draft pin allocation</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str"/>
       <x:c r="C1" s="6" t="str"/>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Board 1 · ATSAMC21G17A-AUT ×3 · 2026-09-06</x:v>
+        <x:v>Board 1 · gateway, three leaves, FTDI and EEPROM · notes reconciled 2026-09-07</x:v>
       </x:c>
       <x:c r="B2" s="6" t="str"/>
       <x:c r="C2" s="6" t="str"/>
@@ -505,10 +505,10 @@
         <x:v>Scope</x:v>
       </x:c>
       <x:c r="B4" s="3" t="str">
-        <x:v>48 physical pads for each leaf. All assignments proposed and evidence unverified. No CAD or hardware validation.</x:v>
+        <x:v>264 pad rows: SAMs 3 × 48, STM32 64, FTDI 48 and EEPROM 8. All allocations remain unverified; no Board 1 CAD exists.</x:v>
       </x:c>
       <x:c r="C4" s="3" t="str">
-        <x:v>B1-R001; B1-Q005; USR-19</x:v>
+        <x:v>B1-R001/005; B1-Q002/005/012; ADR-004/018</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="48" customHeight="1">
@@ -549,10 +549,10 @@
         <x:v>Multidrop circuit</x:v>
       </x:c>
       <x:c r="B8" s="3" t="str">
-        <x:v>TX and RX are separate logical reservations. External open-drain drive/sense circuitry, idle polarity and reset behavior must be designed before connection.</x:v>
+        <x:v>ADR-033/039 select the second LV125 and pulls: TX to /OE, A to GND, Y to UART_MD; RX senses the bus. Reset/ramp behavior and rate remain unqualified.</x:v>
       </x:c>
       <x:c r="C8" s="3" t="str">
-        <x:v>B1-Q003</x:v>
+        <x:v>ADR-033/039; B1-Q003/005</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
@@ -560,10 +560,10 @@
         <x:v>Clock</x:v>
       </x:c>
       <x:c r="B9" s="3" t="str">
-        <x:v>PA14/PA15 pads23/24 are XIN/XOUT. Selected MCU crystal: ECS-120-20-3X-EN-TR. CL 20 pF is crystal load, not the individual capacitor value.</x:v>
+        <x:v>PA14/PA15 pads23/24 are XIN/XOUT. Leaf crystal and initial load capacitors are accepted; see B1-B020/043. Startup/drive/loading remain B1-Q008.</x:v>
       </x:c>
       <x:c r="C9" s="3" t="str">
-        <x:v>ADR-014; B1-Q008</x:v>
+        <x:v>ADR-014/030/031; B1-Q008</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
@@ -571,10 +571,10 @@
         <x:v>Debug</x:v>
       </x:c>
       <x:c r="B10" s="3" t="str">
-        <x:v>PA30 pad45 SWCLK; PA31 pad46 SWDIO; pad40 RESET. Individual 10-pin Cortex SWD header per leaf; exact header and adapter wiring TBD.</x:v>
+        <x:v>PA30/pad45 SWCLK; PA31/pad46 SWDIO; pad40 RESET. SWD header MPN B1-B009 is accepted; numbering, footprint and probe/cable compatibility remain open.</x:v>
       </x:c>
       <x:c r="C10" s="3" t="str">
-        <x:v>ADR-011; B1-Q004/005</x:v>
+        <x:v>ADR-011; ADR-026 (026-reva-connectors.md); B1-Q004/005</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="48" customHeight="1">
@@ -582,10 +582,10 @@
         <x:v>GPIO / LED</x:v>
       </x:c>
       <x:c r="B11" s="3" t="str">
-        <x:v>Four proposed breakouts: PA02, PA03, PB08, PB09. LED PA27. Exact LED current and breakout load/protection remain TBD.</x:v>
+        <x:v>Four GPIOs per MCU and LED/resistor parts are accepted. Leaf pad choices PA02/PA03/PB08/PB09 and LED PA27 remain draft; load/protection and LED drive need review.</x:v>
       </x:c>
       <x:c r="C11" s="3" t="str">
-        <x:v>B1-R019/020; B1-Q010</x:v>
+        <x:v>ADR-029/039; B1-R019/020; B1-Q005/010</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="48" customHeight="1">
@@ -593,10 +593,10 @@
         <x:v>Power</x:v>
       </x:c>
       <x:c r="B12" s="3" t="str">
-        <x:v>3.3 V system intended for VDDIN, VDDIO and VDDANA. VDDCORE is regulator output for its local capacitor only, never tied to 3V3_SYS.</x:v>
+        <x:v>VDDIN/VDDIO/VDDANA use 3V3_SYS. Each VDDCORE has its own accepted ceramic capacitor pair B1-B040/041; never join core outputs or tie them to 3V3_SYS.</x:v>
       </x:c>
       <x:c r="C12" s="3" t="str">
-        <x:v>DS60001479J, §7; ADR-010; B1-Q002/005</x:v>
+        <x:v>ADR-010; ADR-026 (026-sam-core-ceramic.md); ADR-027; B1-Q002/005/011</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
@@ -659,10 +659,10 @@
         <x:v>Crystal source</x:v>
       </x:c>
       <x:c r="B18" s="3" t="str">
-        <x:v>ECS CSM-3X Rev.2017. Smaller crystal remains unverified for MCU startup/drive. Separate accurate FT232HL crystal candidate recorded in project notes.</x:v>
+        <x:v>MCU and separate FTDI crystals are finalized; initial load capacitors are accepted. B1-B014/019/020/042/043/058 own the parts; oscillator qualification remains open.</x:v>
       </x:c>
       <x:c r="C18" s="3" t="str">
-        <x:v>https://ecsxtal.com/store/pdf/CSM-3X.pdf</x:v>
+        <x:v>ADR-014/017/030/031; B1-Q008; https://ecsxtal.com/store/pdf/CSM-3X.pdf</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="48" customHeight="1">
@@ -670,10 +670,10 @@
         <x:v>Stable IDs</x:v>
       </x:c>
       <x:c r="B19" s="3" t="str">
-        <x:v>SAM0 B1-P025–072; SAM1 B1-P073–120; SAM2 B1-P121–168. Parent resource rows retained. Blank parent is represented by NA.</x:v>
+        <x:v>SAM0 B1-P025–072; SAM1 B1-P073–120; SAM2 B1-P121–168; STM32 B1-P169–232; FTDI/EEPROM B1-P233–288. Parent groups B1-P001–024 retained.</x:v>
       </x:c>
       <x:c r="C19" s="3" t="str">
-        <x:v>Board 1 pinmap; next unused ID B1-P169</x:v>
+        <x:v>Board 1 pinmap; next unused ID B1-P289</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="48" customHeight="1">
@@ -681,10 +681,10 @@
         <x:v>Editing</x:v>
       </x:c>
       <x:c r="B20" s="3" t="str">
-        <x:v>Signal/peripheral/mux entries are draft choices. Changing them requires a fresh mux and physical connectivity review. Source references do not mean verified.</x:v>
+        <x:v>Notes reflect ADR-039 baseline. Signal/peripheral/mux choices remain draft. Source citations and accepted MPNs do not establish electrical verification.</x:v>
       </x:c>
       <x:c r="C20" s="3" t="str">
-        <x:v>B1-Q005</x:v>
+        <x:v>B1-Q005; Board 1 unfinished implementation decisions</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1322,7 +1322,7 @@
         <x:v>B1-R003</x:v>
       </x:c>
       <x:c r="J17" s="3" t="str">
-        <x:v>To external open-drain interface TBD. Do not connect push-pull TX directly to shared bus. TXPO=0.</x:v>
+        <x:v>To B1-B066 LV125 /OE; A=GND, Y=UART_MD (ADR-033). /OE pull-up B1-B008 accepted ADR-039. TXPO=0; reset/ramp/timing unverified.</x:v>
       </x:c>
       <x:c r="K17" s="3" t="str">
         <x:v>DS60001479J p.22; 30; 505</x:v>
@@ -1363,7 +1363,7 @@
         <x:v>B1-R003</x:v>
       </x:c>
       <x:c r="J18" s="3" t="str">
-        <x:v>Sense UART_MD through interface TBD. RXPO=1. Rate/pull-up pending B1-Q003.</x:v>
+        <x:v>Sense shared UART_MD; RXPO=1. Bus pull-up B1-B074 accepted ADR-039. Rate, thresholds and rise time remain B1-Q003/005.</x:v>
       </x:c>
       <x:c r="K18" s="3" t="str">
         <x:v>DS60001479J p.22; 30; 505</x:v>
@@ -1732,7 +1732,7 @@
         <x:v>B1-R015</x:v>
       </x:c>
       <x:c r="J27" s="3" t="str">
-        <x:v>ECS-120-20-3X-EN-TR, 12 MHz. CL=20 pF. Load network/startup/drive TBD.</x:v>
+        <x:v>Selected 12 MHz MCU crystal B1-B020; initial load caps B1-B043 accepted ADR-031. Startup, drive and loading remain B1-Q008.</x:v>
       </x:c>
       <x:c r="K27" s="3" t="str">
         <x:v>DS60001479J p.22; 34; 191–192</x:v>
@@ -2388,7 +2388,7 @@
         <x:v>B1-R019</x:v>
       </x:c>
       <x:c r="J43" s="3" t="str">
-        <x:v>Proposed active-high LED. Resistor/current TBD; not counted as spare GPIO.</x:v>
+        <x:v>PA27 LED drive remains proposed. LED and resistor B1-B024/026 accepted ADR-029/039; current/visibility remain B1-Q010.</x:v>
       </x:c>
       <x:c r="K43" s="3" t="str">
         <x:v>DS60001479J p.22; 30</x:v>
@@ -2552,7 +2552,7 @@
         <x:v>B1-R001</x:v>
       </x:c>
       <x:c r="J47" s="3" t="str">
-        <x:v>Regulator output. Local core capacitor only; value per decoupling review. Do not tie to 3.3 V.</x:v>
+        <x:v>Separate regulator output; accepted ceramic pair B1-B040/041, ADR-026 (026-sam-core-ceramic.md)/027. Never join core rails or 3V3_SYS; qualify stability.</x:v>
       </x:c>
       <x:c r="K47" s="3" t="str">
         <x:v>DS60001479J p.22; §7</x:v>
@@ -2776,7 +2776,7 @@
       <x:c r="B55" s="1"/>
       <x:c r="C55" s="1"/>
       <x:c r="D55" s="1" t="str">
-        <x:v>B1-R025 / ADR-032: dedicated 115200 baud; 8N1, no flow control proposed. 1x3 2.54 mm header: 1=MCU TX, 2=MCU RX, 3=GND. No VCC pin. B1-B059/060; B1-Q014.</x:v>
+        <x:v>ADR-032/039: dedicated 115200-baud debug; 1x3 cut header B1-B059 from strip B1-B027. Proposed order 1=MCU TX, 2=MCU RX, 3=GND; 8N1/no flow control. Off-state support B1-B060 remains TBD.</x:v>
       </x:c>
       <x:c r="E55" s="1"/>
       <x:c r="F55" s="1"/>
@@ -2799,7 +2799,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf562bce6464b42ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4be5644386b6422b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3434,7 +3434,7 @@
         <x:v>B1-R003</x:v>
       </x:c>
       <x:c r="J17" s="3" t="str">
-        <x:v>To external open-drain interface TBD. Do not connect push-pull TX directly to shared bus. TXPO=0.</x:v>
+        <x:v>To B1-B066 LV125 /OE; A=GND, Y=UART_MD (ADR-033). /OE pull-up B1-B008 accepted ADR-039. TXPO=0; reset/ramp/timing unverified.</x:v>
       </x:c>
       <x:c r="K17" s="3" t="str">
         <x:v>DS60001479J p.22; 30; 505</x:v>
@@ -3475,7 +3475,7 @@
         <x:v>B1-R003</x:v>
       </x:c>
       <x:c r="J18" s="3" t="str">
-        <x:v>Sense UART_MD through interface TBD. RXPO=1. Rate/pull-up pending B1-Q003.</x:v>
+        <x:v>Sense shared UART_MD; RXPO=1. Bus pull-up B1-B074 accepted ADR-039. Rate, thresholds and rise time remain B1-Q003/005.</x:v>
       </x:c>
       <x:c r="K18" s="3" t="str">
         <x:v>DS60001479J p.22; 30; 505</x:v>
@@ -3844,7 +3844,7 @@
         <x:v>B1-R015</x:v>
       </x:c>
       <x:c r="J27" s="3" t="str">
-        <x:v>ECS-120-20-3X-EN-TR, 12 MHz. CL=20 pF. Load network/startup/drive TBD.</x:v>
+        <x:v>Selected 12 MHz MCU crystal B1-B020; initial load caps B1-B043 accepted ADR-031. Startup, drive and loading remain B1-Q008.</x:v>
       </x:c>
       <x:c r="K27" s="3" t="str">
         <x:v>DS60001479J p.22; 34; 191–192</x:v>
@@ -4500,7 +4500,7 @@
         <x:v>B1-R019</x:v>
       </x:c>
       <x:c r="J43" s="3" t="str">
-        <x:v>Proposed active-high LED. Resistor/current TBD; not counted as spare GPIO.</x:v>
+        <x:v>PA27 LED drive remains proposed. LED and resistor B1-B024/026 accepted ADR-029/039; current/visibility remain B1-Q010.</x:v>
       </x:c>
       <x:c r="K43" s="3" t="str">
         <x:v>DS60001479J p.22; 30</x:v>
@@ -4664,7 +4664,7 @@
         <x:v>B1-R001</x:v>
       </x:c>
       <x:c r="J47" s="3" t="str">
-        <x:v>Regulator output. Local core capacitor only; value per decoupling review. Do not tie to 3.3 V.</x:v>
+        <x:v>Separate regulator output; accepted ceramic pair B1-B040/041, ADR-026 (026-sam-core-ceramic.md)/027. Never join core rails or 3V3_SYS; qualify stability.</x:v>
       </x:c>
       <x:c r="K47" s="3" t="str">
         <x:v>DS60001479J p.22; §7</x:v>
@@ -4888,7 +4888,7 @@
       <x:c r="B55" s="1"/>
       <x:c r="C55" s="1"/>
       <x:c r="D55" s="1" t="str">
-        <x:v>B1-R025 / ADR-032: dedicated 115200 baud; 8N1, no flow control proposed. 1x3 2.54 mm header: 1=MCU TX, 2=MCU RX, 3=GND. No VCC pin. B1-B059/060; B1-Q014.</x:v>
+        <x:v>ADR-032/039: dedicated 115200-baud debug; 1x3 cut header B1-B059 from strip B1-B027. Proposed order 1=MCU TX, 2=MCU RX, 3=GND; 8N1/no flow control. Off-state support B1-B060 remains TBD.</x:v>
       </x:c>
       <x:c r="E55" s="1"/>
       <x:c r="F55" s="1"/>
@@ -4911,7 +4911,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R375edd2720584c9c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55fd92f26cef41fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5546,7 +5546,7 @@
         <x:v>B1-R003</x:v>
       </x:c>
       <x:c r="J17" s="3" t="str">
-        <x:v>To external open-drain interface TBD. Do not connect push-pull TX directly to shared bus. TXPO=0.</x:v>
+        <x:v>To B1-B066 LV125 /OE; A=GND, Y=UART_MD (ADR-033). /OE pull-up B1-B008 accepted ADR-039. TXPO=0; reset/ramp/timing unverified.</x:v>
       </x:c>
       <x:c r="K17" s="3" t="str">
         <x:v>DS60001479J p.22; 30; 505</x:v>
@@ -5587,7 +5587,7 @@
         <x:v>B1-R003</x:v>
       </x:c>
       <x:c r="J18" s="3" t="str">
-        <x:v>Sense UART_MD through interface TBD. RXPO=1. Rate/pull-up pending B1-Q003.</x:v>
+        <x:v>Sense shared UART_MD; RXPO=1. Bus pull-up B1-B074 accepted ADR-039. Rate, thresholds and rise time remain B1-Q003/005.</x:v>
       </x:c>
       <x:c r="K18" s="3" t="str">
         <x:v>DS60001479J p.22; 30; 505</x:v>
@@ -5956,7 +5956,7 @@
         <x:v>B1-R015</x:v>
       </x:c>
       <x:c r="J27" s="3" t="str">
-        <x:v>ECS-120-20-3X-EN-TR, 12 MHz. CL=20 pF. Load network/startup/drive TBD.</x:v>
+        <x:v>Selected 12 MHz MCU crystal B1-B020; initial load caps B1-B043 accepted ADR-031. Startup, drive and loading remain B1-Q008.</x:v>
       </x:c>
       <x:c r="K27" s="3" t="str">
         <x:v>DS60001479J p.22; 34; 191–192</x:v>
@@ -6612,7 +6612,7 @@
         <x:v>B1-R019</x:v>
       </x:c>
       <x:c r="J43" s="3" t="str">
-        <x:v>Proposed active-high LED. Resistor/current TBD; not counted as spare GPIO.</x:v>
+        <x:v>PA27 LED drive remains proposed. LED and resistor B1-B024/026 accepted ADR-029/039; current/visibility remain B1-Q010.</x:v>
       </x:c>
       <x:c r="K43" s="3" t="str">
         <x:v>DS60001479J p.22; 30</x:v>
@@ -6776,7 +6776,7 @@
         <x:v>B1-R001</x:v>
       </x:c>
       <x:c r="J47" s="3" t="str">
-        <x:v>Regulator output. Local core capacitor only; value per decoupling review. Do not tie to 3.3 V.</x:v>
+        <x:v>Separate regulator output; accepted ceramic pair B1-B040/041, ADR-026 (026-sam-core-ceramic.md)/027. Never join core rails or 3V3_SYS; qualify stability.</x:v>
       </x:c>
       <x:c r="K47" s="3" t="str">
         <x:v>DS60001479J p.22; §7</x:v>
@@ -7000,7 +7000,7 @@
       <x:c r="B55" s="1"/>
       <x:c r="C55" s="1"/>
       <x:c r="D55" s="1" t="str">
-        <x:v>B1-R025 / ADR-032: dedicated 115200 baud; 8N1, no flow control proposed. 1x3 2.54 mm header: 1=MCU TX, 2=MCU RX, 3=GND. No VCC pin. B1-B059/060; B1-Q014.</x:v>
+        <x:v>ADR-032/039: dedicated 115200-baud debug; 1x3 cut header B1-B059 from strip B1-B027. Proposed order 1=MCU TX, 2=MCU RX, 3=GND; 8N1/no flow control. Off-state support B1-B060 remains TBD.</x:v>
       </x:c>
       <x:c r="E55" s="1"/>
       <x:c r="F55" s="1"/>
@@ -7023,7 +7023,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78cea3c1951d45d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf988dcbbc324ad8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7330,7 +7330,7 @@
         <x:v>B1-R015</x:v>
       </x:c>
       <x:c r="J9" s="3" t="str">
-        <x:v>12 MHz ECS-120-20-3X-EN-TR. CL=20 pF; individual capacitors TBD.</x:v>
+        <x:v>Selected 12 MHz MCU crystal B1-B019; initial load caps B1-B042 accepted ADR-031. Startup, drive and loading remain B1-Q008.</x:v>
       </x:c>
       <x:c r="K9" s="3" t="str">
         <x:v>DS12288 Rev.6 p.50; 58</x:v>
@@ -8027,7 +8027,7 @@
         <x:v>B1-R019</x:v>
       </x:c>
       <x:c r="J26" s="3" t="str">
-        <x:v>Proposed active-high LED; resistor/current TBD. Not counted as spare GPIO.</x:v>
+        <x:v>PA5 LED drive remains proposed. LED and resistor B1-B024/026 accepted ADR-029/039; current/visibility remain B1-Q010.</x:v>
       </x:c>
       <x:c r="K26" s="3" t="str">
         <x:v>DS12288 Rev.6 p.50; 60</x:v>
@@ -8888,7 +8888,7 @@
         <x:v>B1-R003</x:v>
       </x:c>
       <x:c r="J47" s="3" t="str">
-        <x:v>To open-drain interface TBD. Do not connect push-pull TX directly to shared UART_MD.</x:v>
+        <x:v>To B1-B066 LV125 /OE; A=GND, Y=UART_MD (ADR-033). /OE pull-up B1-B008 accepted ADR-039. Reset/ramp/timing remain unverified.</x:v>
       </x:c>
       <x:c r="K47" s="3" t="str">
         <x:v>DS12288 Rev.6 p.50; 65–66; 73</x:v>
@@ -8929,7 +8929,7 @@
         <x:v>B1-R003</x:v>
       </x:c>
       <x:c r="J48" s="3" t="str">
-        <x:v>Sense shared UART_MD through circuit TBD. Exact rate and idle/reset behavior pending.</x:v>
+        <x:v>Sense shared UART_MD with accepted B1-B074 bus pull-up (ADR-039). Rate, thresholds and idle/reset behavior remain B1-Q003/005.</x:v>
       </x:c>
       <x:c r="K48" s="3" t="str">
         <x:v>DS12288 Rev.6 p.50; 66; 73</x:v>
@@ -9257,7 +9257,7 @@
         <x:v>B1-R016; B1-R021</x:v>
       </x:c>
       <x:c r="J56" s="3" t="str">
-        <x:v>To RS-485 PHY driver input. 12 Mbps ceiling; exact PHY/timing pending B1-Q009.</x:v>
+        <x:v>To selected ST3485EBDR DI. 12 Mbps ceiling retained; actual rate, control timing and remote kit compatibility remain B1-Q009.</x:v>
       </x:c>
       <x:c r="K56" s="3" t="str">
         <x:v>DS12288 Rev.6 p.50; 67; 75</x:v>
@@ -9806,7 +9806,7 @@
       <x:c r="B73" s="1"/>
       <x:c r="C73" s="1"/>
       <x:c r="D73" s="1" t="str">
-        <x:v>Keep PG10 as NRST and PA13/PA14 as SWD. PB8 reserved for BOOT0. Option bytes, probe header/adapter and reset pulls remain B1-Q004/005. SWO is not allocated.</x:v>
+        <x:v>Keep NRST and SWD. ADR-023 allocates CBUS5 to NRST and CBUS6 to BOOT0 through B1-B053 interfaces TBD. Defaults: reset released, BOOT0 low. Option bytes, pulls and probe compatibility remain B1-Q004/005/013.</x:v>
       </x:c>
       <x:c r="E73" s="1"/>
       <x:c r="F73" s="1"/>
@@ -9939,7 +9939,7 @@
       <x:c r="B80" s="1"/>
       <x:c r="C80" s="1"/>
       <x:c r="D80" s="1" t="str">
-        <x:v>B1-P169–B1-P232. B1-P001–006 remain parent groups. RS-485, LED and GPIO rows use requirement references directly. Next pin ID B1-P233.</x:v>
+        <x:v>STM32 B1-P169–232; B1-P001–006 remain parent groups. FTDI/EEPROM use B1-P233–288. Next unused pin ID B1-P289.</x:v>
       </x:c>
       <x:c r="E80" s="1"/>
       <x:c r="F80" s="1"/>
@@ -9958,7 +9958,7 @@
       <x:c r="B83" s="1"/>
       <x:c r="C83" s="1"/>
       <x:c r="D83" s="1" t="str">
-        <x:v>B1-R025 / ADR-032: dedicated 115200 baud; 8N1, no flow control proposed. 1x3 2.54 mm header: 1=MCU TX, 2=MCU RX, 3=GND. No VCC pin. B1-B059/060; B1-Q014.</x:v>
+        <x:v>ADR-032/039: dedicated 115200-baud debug; 1x3 cut header B1-B059 from strip B1-B027. Proposed order 1=MCU TX, 2=MCU RX, 3=GND; 8N1/no flow control. Off-state support B1-B060 remains TBD.</x:v>
       </x:c>
       <x:c r="E83" s="1"/>
       <x:c r="F83" s="1"/>
@@ -9973,7 +9973,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31280dbb229e4ac8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fbca177992f4d36"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10116,7 +10116,7 @@
         <x:v>B1-R005</x:v>
       </x:c>
       <x:c r="J5" s="3" t="str">
-        <x:v>12 MHz B1-B014 candidate per ADR-017. Load capacitors TBD; total accuracy within 30 ppm.</x:v>
+        <x:v>FTDI crystal B1-B014 finalized ADR-030; initial load caps B1-B058 accepted ADR-031. Loading, startup, drive and frequency remain B1-Q008.</x:v>
       </x:c>
       <x:c r="K5" s="3" t="str">
         <x:v>FT_000288 v2.2 p.11; 48</x:v>
@@ -10280,7 +10280,7 @@
         <x:v>B1-R005</x:v>
       </x:c>
       <x:c r="J9" s="3" t="str">
-        <x:v>12 kohm 1% resistor to GND. 0805 proposed; exact resistor in B1-B017 TBD.</x:v>
+        <x:v>Accepted REF resistor B1-B057: 12 kohm 1% to GND (ADR-031). Footprint and circuit qualification remain B1-Q002.</x:v>
       </x:c>
       <x:c r="K9" s="3" t="str">
         <x:v>FT_000288 v2.2 p.11</x:v>
@@ -10567,7 +10567,7 @@
         <x:v>B1-R012</x:v>
       </x:c>
       <x:c r="J16" s="3" t="str">
-        <x:v>Connect to independent VCCD 3.3 V output. All three VCCIO pins required; local bypass B1-B017.</x:v>
+        <x:v>Independent VCCD supply; all three VCCIO pins required. Accepted bypass MPNs B1-B061–063; counts/rail allocation remain B1-Q002.</x:v>
       </x:c>
       <x:c r="K16" s="3" t="str">
         <x:v>FT_000288 v2.2 p.11; 45</x:v>
@@ -10936,7 +10936,7 @@
         <x:v>B1-R012</x:v>
       </x:c>
       <x:c r="J25" s="3" t="str">
-        <x:v>ACBUS0 proposed. To always-powered default-off polarity interface for SC189 EN, per ADR-013.</x:v>
+        <x:v>PWREN# to MC74HC1G14DBVT1G, then TPS560430 EN (ADR-021/024). Pulls B1-B054/055 accepted; startup/default-off qualification remains B1-Q002.</x:v>
       </x:c>
       <x:c r="K25" s="3" t="str">
         <x:v>FT_000288 v2.2 p.12–13</x:v>
@@ -11059,7 +11059,7 @@
         <x:v>B1-R012</x:v>
       </x:c>
       <x:c r="J28" s="3" t="str">
-        <x:v>Connect to independent VCCD 3.3 V output. All three VCCIO pins required; local bypass B1-B017.</x:v>
+        <x:v>Independent VCCD supply; all three VCCIO pins required. Accepted bypass MPNs B1-B061–063; counts/rail allocation remain B1-Q002.</x:v>
       </x:c>
       <x:c r="K28" s="3" t="str">
         <x:v>FT_000288 v2.2 p.11; 45</x:v>
@@ -11469,7 +11469,7 @@
         <x:v>B1-R005; B1-R012</x:v>
       </x:c>
       <x:c r="J38" s="3" t="str">
-        <x:v>Independent bridge reset. Pull-up/RC or supervisor TBD under B1-Q002; allow EEPROM startup before read.</x:v>
+        <x:v>RESET# uses accepted pull-up B1-B051 and capacitor B1-B064 (ADR-022/027/028). No external supervisor. EEPROM startup/ramp checks B1-Q002/012.</x:v>
       </x:c>
       <x:c r="K38" s="3" t="str">
         <x:v>FT_000288 v2.2 p.11; §4.11</x:v>
@@ -11715,7 +11715,7 @@
         <x:v>B1-R012</x:v>
       </x:c>
       <x:c r="J44" s="3" t="str">
-        <x:v>From USB-B protected supply before SC189. Local bypass/inrush budget B1-B017/B1-Q002.</x:v>
+        <x:v>From ramped USB_5V after TPS22810, shared with buck VIN (ADR-021/022). USB_5V_PROTECTED is this workbook alias. Bypass counts B1-B061–063 TBD.</x:v>
       </x:c>
       <x:c r="K44" s="3" t="str">
         <x:v>FT_000288 v2.2 p.11; 45</x:v>
@@ -11838,7 +11838,7 @@
         <x:v>B1-R005; B1-R012</x:v>
       </x:c>
       <x:c r="J47" s="3" t="str">
-        <x:v>Direct to EEPROM DI/pad 3; DO/pad 4 through 2.2 kohm. DO side has 10 kohm pull-up to 3V3_FTDI.</x:v>
+        <x:v>EEDATA to EEPROM DI directly; DO via accepted B1-B056; DO-side pull-up B1-B065 to 3V3_FTDI. ADR-028/030; timing/startup remain B1-Q012.</x:v>
       </x:c>
       <x:c r="K47" s="3" t="str">
         <x:v>FT_000288 v2.2 p.12; 49 Fig.7.1</x:v>
@@ -11961,7 +11961,7 @@
         <x:v>B1-R012</x:v>
       </x:c>
       <x:c r="J50" s="3" t="str">
-        <x:v>Connect to independent VCCD 3.3 V output. All three VCCIO pins required; local bypass B1-B017.</x:v>
+        <x:v>Independent VCCD supply; all three VCCIO pins required. Accepted bypass MPNs B1-B061–063; counts/rail allocation remain B1-Q002.</x:v>
       </x:c>
       <x:c r="K50" s="3" t="str">
         <x:v>FT_000288 v2.2 p.11; 45</x:v>
@@ -12310,7 +12310,7 @@
         <x:v>B1-R005; B1-R012</x:v>
       </x:c>
       <x:c r="J61" s="3" t="str">
-        <x:v>To EEDATA through 2.2 kohm; 10 kohm pull-up on DO side to 3V3_FTDI.</x:v>
+        <x:v>DO to EEDATA via accepted B1-B056; DO-side pull-up B1-B065 to 3V3_FTDI. ADR-028/030; timing remains B1-Q012.</x:v>
       </x:c>
       <x:c r="K61" s="3" t="str">
         <x:v>DS20006260B p.3–9; 31</x:v>
@@ -12474,7 +12474,7 @@
         <x:v>B1-R005; B1-R012</x:v>
       </x:c>
       <x:c r="J65" s="3" t="str">
-        <x:v>From FT232HL VCCD/pad 39. Propose 100 nF local 0805 bypass in B1-B017. Startup constraints B1-Q012.</x:v>
+        <x:v>From FT232HL VCCD. Local bypass belongs to accepted B1-B061 allocation; final count and startup constraints remain B1-Q002/012.</x:v>
       </x:c>
       <x:c r="K65" s="3" t="str">
         <x:v>DS20006260B p.3–9; 31</x:v>
@@ -12531,7 +12531,7 @@
       <x:c r="B70" s="1"/>
       <x:c r="C70" s="1"/>
       <x:c r="D70" s="1" t="str">
-        <x:v>Program/read back EEPROM, then re-enumerate. Blank or corrupt EEPROM must leave SC189 EN off. Pull-down-in-suspend policy and receiver pulls require review.</x:v>
+        <x:v>Program/read back and re-enumerate. Blank/corrupt EEPROM must keep TPS560430 EN off through the accepted inverter/pulls. Suspend defaults and receiver pulls remain B1-Q002.</x:v>
       </x:c>
       <x:c r="E70" s="1"/>
       <x:c r="F70" s="1"/>
@@ -12588,7 +12588,7 @@
       <x:c r="B73" s="1"/>
       <x:c r="C73" s="1"/>
       <x:c r="D73" s="1" t="str">
-        <x:v>EEPROM and FTDI bypass/filter parts belong to B1-B017, separate from main-rail capacitance. VCCA and VCORE each have their own 100 nF only.</x:v>
+        <x:v>Bridge caps B1-B061–063 have accepted MPNs but TBD counts; split support B1-B051/054–058/064/065 is excluded from residual B1-B017. 3V3_FTDI aliases FTDI_3V3; VCCA/VCORE stay separate.</x:v>
       </x:c>
       <x:c r="E73" s="1"/>
       <x:c r="F73" s="1"/>
@@ -12626,7 +12626,7 @@
       <x:c r="B75" s="1"/>
       <x:c r="C75" s="1"/>
       <x:c r="D75" s="1" t="str">
-        <x:v>B1-Q002/008/012: power, default-off logic, SN74LV125 logic levels and 12 Mbaud timing, crystal, EEPROM startup/clock, exact support parts and footprints. No ERC/DRC or bench validation.</x:v>
+        <x:v>B1-Q002/008/012/013: rails, enables/defaults, VCP timing, oscillator/EEPROM qualification and CBUS interfaces. Selected parts remain accepted; all pad evidence stays unverified.</x:v>
       </x:c>
       <x:c r="E75" s="1"/>
       <x:c r="F75" s="1"/>
@@ -12679,8 +12679,8 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R721a2ff0085746ed"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R850ee3d52e964b21"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f7559dc01174432"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6eeac784a8cc4dcd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/samc21-pin-allocation/samc21_pin_allocation.xlsx
+++ b/outputs/samc21-pin-allocation/samc21_pin_allocation.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R7203cc0b85584988"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAM0" sheetId="2" r:id="R6f9f200a0a5a4d68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAM1" sheetId="3" r:id="R2efb696a4a57481a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAM2" sheetId="4" r:id="R6c8137ec712c4a86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STM32" sheetId="5" r:id="R037ca390c10d46fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FTDI" sheetId="6" r:id="R11c7b9a793ea4e7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rd62105511ec04276"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAM0" sheetId="2" r:id="Ra95331f3afd04a8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAM1" sheetId="3" r:id="R2754fb636f6d4fbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAM2" sheetId="4" r:id="R01ad8cdfad4c4571"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STM32" sheetId="5" r:id="R706c7d5b7fd94946"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FTDI" sheetId="6" r:id="Rc5b64abebf824b07"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -579,13 +579,13 @@
     </x:row>
     <x:row r="11" ht="48" customHeight="1">
       <x:c r="A11" s="3" t="str">
-        <x:v>GPIO / LED</x:v>
+        <x:v>Timing / LED</x:v>
       </x:c>
       <x:c r="B11" s="3" t="str">
-        <x:v>Four GPIOs per MCU and LED/resistor parts are accepted. Leaf pad choices PA02/PA03/PB08/PB09 and LED PA27 remain draft; load/protection and LED drive need review.</x:v>
+        <x:v>One LED per MCU; combined timing/debug headers per ADR-041. Timing pad assignment TBD.</x:v>
       </x:c>
       <x:c r="C11" s="3" t="str">
-        <x:v>ADR-029/039; B1-R019/020; B1-Q005/010</x:v>
+        <x:v>ADR-041; B1-R019/027</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="48" customHeight="1">
@@ -894,25 +894,25 @@
         <x:v>PA02</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
-        <x:v>GPIO_1</x:v>
+        <x:v>TEST_IO_TBD</x:v>
       </x:c>
       <x:c r="E7" s="9" t="str">
-        <x:v>PORT</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="F7" s="9" t="str">
-        <x:v>GPIO</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="G7" s="3" t="str">
-        <x:v>I/O</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="H7" s="3" t="str">
         <x:v>NA</x:v>
       </x:c>
       <x:c r="I7" s="3" t="str">
-        <x:v>B1-R020</x:v>
+        <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J7" s="3" t="str">
-        <x:v>Proposed breakout. Load/protection contract TBD.</x:v>
+        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
       </x:c>
       <x:c r="K7" s="3" t="str">
         <x:v>DS60001479J p.22; 29</x:v>
@@ -935,25 +935,25 @@
         <x:v>PA03</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>GPIO_2</x:v>
+        <x:v>TEST_IO_TBD</x:v>
       </x:c>
       <x:c r="E8" s="9" t="str">
-        <x:v>PORT</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="F8" s="9" t="str">
-        <x:v>GPIO</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="G8" s="3" t="str">
-        <x:v>I/O</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="H8" s="3" t="str">
         <x:v>NA</x:v>
       </x:c>
       <x:c r="I8" s="3" t="str">
-        <x:v>B1-R020</x:v>
+        <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J8" s="3" t="str">
-        <x:v>Proposed breakout. No external analog reference required.</x:v>
+        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
       </x:c>
       <x:c r="K8" s="3" t="str">
         <x:v>DS60001479J p.22; 29</x:v>
@@ -1058,25 +1058,25 @@
         <x:v>PB08</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
-        <x:v>GPIO_3</x:v>
+        <x:v>TEST_IO_TBD</x:v>
       </x:c>
       <x:c r="E11" s="9" t="str">
-        <x:v>PORT</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="F11" s="9" t="str">
-        <x:v>GPIO</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="G11" s="3" t="str">
-        <x:v>I/O</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="H11" s="3" t="str">
         <x:v>NA</x:v>
       </x:c>
       <x:c r="I11" s="3" t="str">
-        <x:v>B1-R020</x:v>
+        <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J11" s="3" t="str">
-        <x:v>Proposed breakout. Load/protection contract TBD.</x:v>
+        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
       </x:c>
       <x:c r="K11" s="3" t="str">
         <x:v>DS60001479J p.22; 29</x:v>
@@ -1099,25 +1099,25 @@
         <x:v>PB09</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>GPIO_4</x:v>
+        <x:v>TEST_IO_TBD</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
-        <x:v>PORT</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="F12" s="9" t="str">
-        <x:v>GPIO</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="G12" s="3" t="str">
-        <x:v>I/O</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="H12" s="3" t="str">
         <x:v>NA</x:v>
       </x:c>
       <x:c r="I12" s="3" t="str">
-        <x:v>B1-R020</x:v>
+        <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J12" s="3" t="str">
-        <x:v>Proposed breakout. Load/protection contract TBD.</x:v>
+        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
       </x:c>
       <x:c r="K12" s="3" t="str">
         <x:v>DS60001479J p.22; 29</x:v>
@@ -1650,7 +1650,7 @@
         <x:v>B1-R025</x:v>
       </x:c>
       <x:c r="J25" s="3" t="str">
-        <x:v>115200 baud; 8N1 proposed. Header pin 1 TX to adapter RX; pin 3 GND. 3.3 V logic. Off-state interface TBD B1-Q014.</x:v>
+        <x:v>Header pin 2: MCU TX to adapter RX via 330 ohm near MCU. GND pins 3/6. 115200 baud, 3.3 V. ADR-042; B1-Q014.</x:v>
       </x:c>
       <x:c r="K25" s="3" t="str">
         <x:v>DS60001479J pp.22,30; USART CTRLA p.505</x:v>
@@ -1691,7 +1691,7 @@
         <x:v>B1-R025</x:v>
       </x:c>
       <x:c r="J26" s="3" t="str">
-        <x:v>115200 baud; 8N1 proposed. Header pin 2 RX from adapter TX; pin 3 GND. 3.3 V logic. Off-state interface TBD B1-Q014.</x:v>
+        <x:v>Header pin 1: MCU RX from adapter TX via 330 ohm near MCU. GND pins 3/6. 115200 baud, 3.3 V. ADR-042; B1-Q014.</x:v>
       </x:c>
       <x:c r="K26" s="3" t="str">
         <x:v>DS60001479J pp.22,30; USART CTRLA p.505</x:v>
@@ -2776,7 +2776,7 @@
       <x:c r="B55" s="1"/>
       <x:c r="C55" s="1"/>
       <x:c r="D55" s="1" t="str">
-        <x:v>ADR-032/039: dedicated 115200-baud debug; 1x3 cut header B1-B059 from strip B1-B027. Proposed order 1=MCU TX, 2=MCU RX, 3=GND; 8N1/no flow control. Off-state support B1-B060 remains TBD.</x:v>
+        <x:v>ADR-041: one 1x8 timing/debug header per MCU. RX, TX, GND, SYNC, TRIG, GND, EVENT0, EVENT1. Timing MCU pads TBD; debug UART mapping retained.</x:v>
       </x:c>
       <x:c r="E55" s="1"/>
       <x:c r="F55" s="1"/>
@@ -2799,7 +2799,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4be5644386b6422b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f726f3bc1c54f39"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3006,25 +3006,25 @@
         <x:v>PA02</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
-        <x:v>GPIO_1</x:v>
+        <x:v>TEST_IO_TBD</x:v>
       </x:c>
       <x:c r="E7" s="9" t="str">
-        <x:v>PORT</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="F7" s="9" t="str">
-        <x:v>GPIO</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="G7" s="3" t="str">
-        <x:v>I/O</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="H7" s="3" t="str">
         <x:v>NA</x:v>
       </x:c>
       <x:c r="I7" s="3" t="str">
-        <x:v>B1-R020</x:v>
+        <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J7" s="3" t="str">
-        <x:v>Proposed breakout. Load/protection contract TBD.</x:v>
+        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
       </x:c>
       <x:c r="K7" s="3" t="str">
         <x:v>DS60001479J p.22; 29</x:v>
@@ -3047,25 +3047,25 @@
         <x:v>PA03</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>GPIO_2</x:v>
+        <x:v>TEST_IO_TBD</x:v>
       </x:c>
       <x:c r="E8" s="9" t="str">
-        <x:v>PORT</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="F8" s="9" t="str">
-        <x:v>GPIO</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="G8" s="3" t="str">
-        <x:v>I/O</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="H8" s="3" t="str">
         <x:v>NA</x:v>
       </x:c>
       <x:c r="I8" s="3" t="str">
-        <x:v>B1-R020</x:v>
+        <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J8" s="3" t="str">
-        <x:v>Proposed breakout. No external analog reference required.</x:v>
+        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
       </x:c>
       <x:c r="K8" s="3" t="str">
         <x:v>DS60001479J p.22; 29</x:v>
@@ -3170,25 +3170,25 @@
         <x:v>PB08</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
-        <x:v>GPIO_3</x:v>
+        <x:v>TEST_IO_TBD</x:v>
       </x:c>
       <x:c r="E11" s="9" t="str">
-        <x:v>PORT</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="F11" s="9" t="str">
-        <x:v>GPIO</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="G11" s="3" t="str">
-        <x:v>I/O</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="H11" s="3" t="str">
         <x:v>NA</x:v>
       </x:c>
       <x:c r="I11" s="3" t="str">
-        <x:v>B1-R020</x:v>
+        <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J11" s="3" t="str">
-        <x:v>Proposed breakout. Load/protection contract TBD.</x:v>
+        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
       </x:c>
       <x:c r="K11" s="3" t="str">
         <x:v>DS60001479J p.22; 29</x:v>
@@ -3211,25 +3211,25 @@
         <x:v>PB09</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>GPIO_4</x:v>
+        <x:v>TEST_IO_TBD</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
-        <x:v>PORT</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="F12" s="9" t="str">
-        <x:v>GPIO</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="G12" s="3" t="str">
-        <x:v>I/O</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="H12" s="3" t="str">
         <x:v>NA</x:v>
       </x:c>
       <x:c r="I12" s="3" t="str">
-        <x:v>B1-R020</x:v>
+        <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J12" s="3" t="str">
-        <x:v>Proposed breakout. Load/protection contract TBD.</x:v>
+        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
       </x:c>
       <x:c r="K12" s="3" t="str">
         <x:v>DS60001479J p.22; 29</x:v>
@@ -3762,7 +3762,7 @@
         <x:v>B1-R025</x:v>
       </x:c>
       <x:c r="J25" s="3" t="str">
-        <x:v>115200 baud; 8N1 proposed. Header pin 1 TX to adapter RX; pin 3 GND. 3.3 V logic. Off-state interface TBD B1-Q014.</x:v>
+        <x:v>Header pin 2: MCU TX to adapter RX via 330 ohm near MCU. GND pins 3/6. 115200 baud, 3.3 V. ADR-042; B1-Q014.</x:v>
       </x:c>
       <x:c r="K25" s="3" t="str">
         <x:v>DS60001479J pp.22,30; USART CTRLA p.505</x:v>
@@ -3803,7 +3803,7 @@
         <x:v>B1-R025</x:v>
       </x:c>
       <x:c r="J26" s="3" t="str">
-        <x:v>115200 baud; 8N1 proposed. Header pin 2 RX from adapter TX; pin 3 GND. 3.3 V logic. Off-state interface TBD B1-Q014.</x:v>
+        <x:v>Header pin 1: MCU RX from adapter TX via 330 ohm near MCU. GND pins 3/6. 115200 baud, 3.3 V. ADR-042; B1-Q014.</x:v>
       </x:c>
       <x:c r="K26" s="3" t="str">
         <x:v>DS60001479J pp.22,30; USART CTRLA p.505</x:v>
@@ -4888,7 +4888,7 @@
       <x:c r="B55" s="1"/>
       <x:c r="C55" s="1"/>
       <x:c r="D55" s="1" t="str">
-        <x:v>ADR-032/039: dedicated 115200-baud debug; 1x3 cut header B1-B059 from strip B1-B027. Proposed order 1=MCU TX, 2=MCU RX, 3=GND; 8N1/no flow control. Off-state support B1-B060 remains TBD.</x:v>
+        <x:v>ADR-041: one 1x8 timing/debug header per MCU. RX, TX, GND, SYNC, TRIG, GND, EVENT0, EVENT1. Timing MCU pads TBD; debug UART mapping retained.</x:v>
       </x:c>
       <x:c r="E55" s="1"/>
       <x:c r="F55" s="1"/>
@@ -4911,7 +4911,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55fd92f26cef41fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8affdae8a57a4e1a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5118,25 +5118,25 @@
         <x:v>PA02</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
-        <x:v>GPIO_1</x:v>
+        <x:v>TEST_IO_TBD</x:v>
       </x:c>
       <x:c r="E7" s="9" t="str">
-        <x:v>PORT</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="F7" s="9" t="str">
-        <x:v>GPIO</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="G7" s="3" t="str">
-        <x:v>I/O</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="H7" s="3" t="str">
         <x:v>NA</x:v>
       </x:c>
       <x:c r="I7" s="3" t="str">
-        <x:v>B1-R020</x:v>
+        <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J7" s="3" t="str">
-        <x:v>Proposed breakout. Load/protection contract TBD.</x:v>
+        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
       </x:c>
       <x:c r="K7" s="3" t="str">
         <x:v>DS60001479J p.22; 29</x:v>
@@ -5159,25 +5159,25 @@
         <x:v>PA03</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>GPIO_2</x:v>
+        <x:v>TEST_IO_TBD</x:v>
       </x:c>
       <x:c r="E8" s="9" t="str">
-        <x:v>PORT</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="F8" s="9" t="str">
-        <x:v>GPIO</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="G8" s="3" t="str">
-        <x:v>I/O</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="H8" s="3" t="str">
         <x:v>NA</x:v>
       </x:c>
       <x:c r="I8" s="3" t="str">
-        <x:v>B1-R020</x:v>
+        <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J8" s="3" t="str">
-        <x:v>Proposed breakout. No external analog reference required.</x:v>
+        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
       </x:c>
       <x:c r="K8" s="3" t="str">
         <x:v>DS60001479J p.22; 29</x:v>
@@ -5282,25 +5282,25 @@
         <x:v>PB08</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
-        <x:v>GPIO_3</x:v>
+        <x:v>TEST_IO_TBD</x:v>
       </x:c>
       <x:c r="E11" s="9" t="str">
-        <x:v>PORT</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="F11" s="9" t="str">
-        <x:v>GPIO</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="G11" s="3" t="str">
-        <x:v>I/O</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="H11" s="3" t="str">
         <x:v>NA</x:v>
       </x:c>
       <x:c r="I11" s="3" t="str">
-        <x:v>B1-R020</x:v>
+        <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J11" s="3" t="str">
-        <x:v>Proposed breakout. Load/protection contract TBD.</x:v>
+        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
       </x:c>
       <x:c r="K11" s="3" t="str">
         <x:v>DS60001479J p.22; 29</x:v>
@@ -5323,25 +5323,25 @@
         <x:v>PB09</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>GPIO_4</x:v>
+        <x:v>TEST_IO_TBD</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
-        <x:v>PORT</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="F12" s="9" t="str">
-        <x:v>GPIO</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="G12" s="3" t="str">
-        <x:v>I/O</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="H12" s="3" t="str">
         <x:v>NA</x:v>
       </x:c>
       <x:c r="I12" s="3" t="str">
-        <x:v>B1-R020</x:v>
+        <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J12" s="3" t="str">
-        <x:v>Proposed breakout. Load/protection contract TBD.</x:v>
+        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
       </x:c>
       <x:c r="K12" s="3" t="str">
         <x:v>DS60001479J p.22; 29</x:v>
@@ -5874,7 +5874,7 @@
         <x:v>B1-R025</x:v>
       </x:c>
       <x:c r="J25" s="3" t="str">
-        <x:v>115200 baud; 8N1 proposed. Header pin 1 TX to adapter RX; pin 3 GND. 3.3 V logic. Off-state interface TBD B1-Q014.</x:v>
+        <x:v>Header pin 2: MCU TX to adapter RX via 330 ohm near MCU. GND pins 3/6. 115200 baud, 3.3 V. ADR-042; B1-Q014.</x:v>
       </x:c>
       <x:c r="K25" s="3" t="str">
         <x:v>DS60001479J pp.22,30; USART CTRLA p.505</x:v>
@@ -5915,7 +5915,7 @@
         <x:v>B1-R025</x:v>
       </x:c>
       <x:c r="J26" s="3" t="str">
-        <x:v>115200 baud; 8N1 proposed. Header pin 2 RX from adapter TX; pin 3 GND. 3.3 V logic. Off-state interface TBD B1-Q014.</x:v>
+        <x:v>Header pin 1: MCU RX from adapter TX via 330 ohm near MCU. GND pins 3/6. 115200 baud, 3.3 V. ADR-042; B1-Q014.</x:v>
       </x:c>
       <x:c r="K26" s="3" t="str">
         <x:v>DS60001479J pp.22,30; USART CTRLA p.505</x:v>
@@ -7000,7 +7000,7 @@
       <x:c r="B55" s="1"/>
       <x:c r="C55" s="1"/>
       <x:c r="D55" s="1" t="str">
-        <x:v>ADR-032/039: dedicated 115200-baud debug; 1x3 cut header B1-B059 from strip B1-B027. Proposed order 1=MCU TX, 2=MCU RX, 3=GND; 8N1/no flow control. Off-state support B1-B060 remains TBD.</x:v>
+        <x:v>ADR-041: one 1x8 timing/debug header per MCU. RX, TX, GND, SYNC, TRIG, GND, EVENT0, EVENT1. Timing MCU pads TBD; debug UART mapping retained.</x:v>
       </x:c>
       <x:c r="E55" s="1"/>
       <x:c r="F55" s="1"/>
@@ -7023,7 +7023,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf988dcbbc324ad8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fcd677ece3c4e87"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7412,7 +7412,7 @@
         <x:v>B1-R007</x:v>
       </x:c>
       <x:c r="J11" s="3" t="str">
-        <x:v>Cortex SWD nRESET plus FTDI ACBUS5/pad 29 via open-drain interface TBD. Preserve NRST; default released. B1-R024; B1-Q013.</x:v>
+        <x:v>Independent SWD nRESET. Preserve NRST reset function and default released. No CBUS connection in Rev A (ADR-042); B1-Q005.</x:v>
       </x:c>
       <x:c r="K11" s="3" t="str">
         <x:v>DS12288 Rev.6 p.50; 58; 72</x:v>
@@ -7435,25 +7435,25 @@
         <x:v>PC0</x:v>
       </x:c>
       <x:c r="D12" s="13" t="str">
-        <x:v>GPIO_1</x:v>
+        <x:v>TEST_IO_TBD</x:v>
       </x:c>
       <x:c r="E12" s="13" t="str">
-        <x:v>GPIO</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="F12" s="13" t="str">
-        <x:v>GPIO</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="G12" s="3" t="str">
-        <x:v>I/O</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="H12" s="3" t="str">
         <x:v>NA</x:v>
       </x:c>
       <x:c r="I12" s="3" t="str">
-        <x:v>B1-R020</x:v>
+        <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J12" s="3" t="str">
-        <x:v>Proposed breakout. Load/protection contract TBD. Keep routing away from crystal.</x:v>
+        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
       </x:c>
       <x:c r="K12" s="3" t="str">
         <x:v>DS12288 Rev.6 p.50; 58–59; 75</x:v>
@@ -7476,25 +7476,25 @@
         <x:v>PC1</x:v>
       </x:c>
       <x:c r="D13" s="13" t="str">
-        <x:v>GPIO_2</x:v>
+        <x:v>TEST_IO_TBD</x:v>
       </x:c>
       <x:c r="E13" s="13" t="str">
-        <x:v>GPIO</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="F13" s="13" t="str">
-        <x:v>GPIO</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="G13" s="3" t="str">
-        <x:v>I/O</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="H13" s="3" t="str">
         <x:v>NA</x:v>
       </x:c>
       <x:c r="I13" s="3" t="str">
-        <x:v>B1-R020</x:v>
+        <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J13" s="3" t="str">
-        <x:v>Proposed breakout. Load/protection contract TBD. Keep routing away from crystal.</x:v>
+        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
       </x:c>
       <x:c r="K13" s="3" t="str">
         <x:v>DS12288 Rev.6 p.50; 58–59; 75</x:v>
@@ -7517,25 +7517,25 @@
         <x:v>PC2</x:v>
       </x:c>
       <x:c r="D14" s="13" t="str">
-        <x:v>GPIO_3</x:v>
+        <x:v>TEST_IO_TBD</x:v>
       </x:c>
       <x:c r="E14" s="13" t="str">
-        <x:v>GPIO</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="F14" s="13" t="str">
-        <x:v>GPIO</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="G14" s="3" t="str">
-        <x:v>I/O</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="H14" s="3" t="str">
         <x:v>NA</x:v>
       </x:c>
       <x:c r="I14" s="3" t="str">
-        <x:v>B1-R020</x:v>
+        <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J14" s="3" t="str">
-        <x:v>Proposed breakout. Load/protection contract TBD. Keep routing away from crystal.</x:v>
+        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
       </x:c>
       <x:c r="K14" s="3" t="str">
         <x:v>DS12288 Rev.6 p.50; 58–59; 75</x:v>
@@ -7558,25 +7558,25 @@
         <x:v>PC3</x:v>
       </x:c>
       <x:c r="D15" s="13" t="str">
-        <x:v>GPIO_4</x:v>
+        <x:v>TEST_IO_TBD</x:v>
       </x:c>
       <x:c r="E15" s="13" t="str">
-        <x:v>GPIO</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="F15" s="13" t="str">
-        <x:v>GPIO</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="G15" s="3" t="str">
-        <x:v>I/O</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="H15" s="3" t="str">
         <x:v>NA</x:v>
       </x:c>
       <x:c r="I15" s="3" t="str">
-        <x:v>B1-R020</x:v>
+        <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J15" s="3" t="str">
-        <x:v>Proposed breakout. Load/protection contract TBD. Keep routing away from crystal.</x:v>
+        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
       </x:c>
       <x:c r="K15" s="3" t="str">
         <x:v>DS12288 Rev.6 p.50; 58–59; 75</x:v>
@@ -8355,7 +8355,7 @@
         <x:v>B1-R025</x:v>
       </x:c>
       <x:c r="J34" s="3" t="str">
-        <x:v>115200 baud; 8N1 proposed. Header pin 2 RX from adapter TX; pin 3 GND. 3.3 V logic. Off-state interface TBD B1-Q014.</x:v>
+        <x:v>Header pin 1: MCU RX from adapter TX via 330 ohm near MCU. GND pins 3/6. 115200 baud, 3.3 V. ADR-042; B1-Q014.</x:v>
       </x:c>
       <x:c r="K34" s="3" t="str">
         <x:v>DS12288 Rev.6 pp.50,63,74</x:v>
@@ -8478,7 +8478,7 @@
         <x:v>B1-R025</x:v>
       </x:c>
       <x:c r="J37" s="3" t="str">
-        <x:v>115200 baud; 8N1 proposed. Header pin 1 TX to adapter RX; pin 3 GND. 3.3 V logic. Off-state interface TBD B1-Q014.</x:v>
+        <x:v>Header pin 2: MCU TX to adapter RX via 330 ohm near MCU. GND pins 3/6. 115200 baud, 3.3 V. ADR-042; B1-Q014.</x:v>
       </x:c>
       <x:c r="K37" s="3" t="str">
         <x:v>DS12288 Rev.6 pp.50,63,74</x:v>
@@ -9626,7 +9626,7 @@
         <x:v>B1-R001</x:v>
       </x:c>
       <x:c r="J65" s="3" t="str">
-        <x:v>FTDI ACBUS6/pad 30 via interface TBD. Default BOOT0 low. nSWBOOT0=1, nBOOT1=1, BOOT_LOCK=0 for pin boot. B1-R024; B1-Q013.</x:v>
+        <x:v>Default BOOT0 low; ordinary boot support B1-B010. Verify normal-boot option bytes B1-Q005. No CBUS connection in Rev A (ADR-042).</x:v>
       </x:c>
       <x:c r="K65" s="3" t="str">
         <x:v>DS12288 Rev.6 p.50; 71; §3.7</x:v>
@@ -9806,7 +9806,7 @@
       <x:c r="B73" s="1"/>
       <x:c r="C73" s="1"/>
       <x:c r="D73" s="1" t="str">
-        <x:v>Keep NRST and SWD. ADR-023 allocates CBUS5 to NRST and CBUS6 to BOOT0 through B1-B053 interfaces TBD. Defaults: reset released, BOOT0 low. Option bytes, pulls and probe compatibility remain B1-Q004/005/013.</x:v>
+        <x:v>Keep NRST/SWD and BOOT0-low defaults (B1-B010). Automated CBUS reset/BOOT0 deferred to Rev B, ADR-042. Reset support/option bytes remain B1-Q005.</x:v>
       </x:c>
       <x:c r="E73" s="1"/>
       <x:c r="F73" s="1"/>
@@ -9958,7 +9958,7 @@
       <x:c r="B83" s="1"/>
       <x:c r="C83" s="1"/>
       <x:c r="D83" s="1" t="str">
-        <x:v>ADR-032/039: dedicated 115200-baud debug; 1x3 cut header B1-B059 from strip B1-B027. Proposed order 1=MCU TX, 2=MCU RX, 3=GND; 8N1/no flow control. Off-state support B1-B060 remains TBD.</x:v>
+        <x:v>ADR-041: one 1x8 timing/debug header per MCU. RX, TX, GND, SYNC, TRIG, GND, EVENT0, EVENT1. Timing MCU pads TBD; debug UART mapping retained.</x:v>
       </x:c>
       <x:c r="E83" s="1"/>
       <x:c r="F83" s="1"/>
@@ -9973,7 +9973,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fbca177992f4d36"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R646175e736c04cb7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11246,25 +11246,25 @@
         <x:v>ACBUS5</x:v>
       </x:c>
       <x:c r="D33" s="17" t="str">
-        <x:v>GW_RESET_CTRL</x:v>
+        <x:v>UNUSED</x:v>
       </x:c>
       <x:c r="E33" s="17" t="str">
-        <x:v>Gateway reset</x:v>
+        <x:v>ACBUS</x:v>
       </x:c>
       <x:c r="F33" s="17" t="str">
-        <x:v>EEPROM GPIO</x:v>
+        <x:v>TriSt-PU</x:v>
       </x:c>
       <x:c r="G33" s="3" t="str">
-        <x:v>Out</x:v>
+        <x:v>In</x:v>
       </x:c>
       <x:c r="H33" s="3" t="str">
         <x:v>NA</x:v>
       </x:c>
       <x:c r="I33" s="3" t="str">
-        <x:v>B1-R024; B1-R007</x:v>
+        <x:v>B1-R005</x:v>
       </x:c>
       <x:c r="J33" s="3" t="str">
-        <x:v>To STM32 NRST/pad 7 through power-off-safe open-drain interface TBD (B1-B053). Polarity TBD; default reset released. B1-Q013.</x:v>
+        <x:v>Leave unconnected in Rev A. Automated recovery deferred to Rev B by ADR-042; no B1-B053 parts or footprints.</x:v>
       </x:c>
       <x:c r="K33" s="3" t="str">
         <x:v>FT_000288 v2.2 p.12–13</x:v>
@@ -11287,25 +11287,25 @@
         <x:v>ACBUS6</x:v>
       </x:c>
       <x:c r="D34" s="17" t="str">
-        <x:v>GW_BOOT0_CTRL</x:v>
+        <x:v>UNUSED</x:v>
       </x:c>
       <x:c r="E34" s="17" t="str">
-        <x:v>Gateway boot</x:v>
+        <x:v>ACBUS</x:v>
       </x:c>
       <x:c r="F34" s="17" t="str">
-        <x:v>EEPROM GPIO</x:v>
+        <x:v>TriSt-PU</x:v>
       </x:c>
       <x:c r="G34" s="3" t="str">
-        <x:v>Out</x:v>
+        <x:v>In</x:v>
       </x:c>
       <x:c r="H34" s="3" t="str">
         <x:v>NA</x:v>
       </x:c>
       <x:c r="I34" s="3" t="str">
-        <x:v>B1-R024</x:v>
+        <x:v>B1-R005</x:v>
       </x:c>
       <x:c r="J34" s="3" t="str">
-        <x:v>To STM32 PB8/BOOT0 pad 61 through power-off-safe interface TBD (B1-B053). Polarity TBD; default BOOT0 low. B1-Q013.</x:v>
+        <x:v>Leave unconnected in Rev A. Automated recovery deferred to Rev B by ADR-042; no B1-B053 parts or footprints.</x:v>
       </x:c>
       <x:c r="K34" s="3" t="str">
         <x:v>FT_000288 v2.2 p.12–13</x:v>
@@ -12512,7 +12512,7 @@
       <x:c r="B69" s="1"/>
       <x:c r="C69" s="1"/>
       <x:c r="D69" s="1" t="str">
-        <x:v>FT_Prog: UART/VCP, bus-powered, ACBUS0=PWREN#, ACBUS5/6=GPIO, other unused ACBUS=TriSt-PU except ACBUS7. Remote wake and Suspend on ACBUS7 Low off.</x:v>
+        <x:v>FT_Prog: UART/VCP, bus-powered, ACBUS0=PWREN#. Unused ACBUS5/6: TriSt-PU, unconnected (ADR-042). Retain other unused-pin policy; remote wake and Suspend on ACBUS7 Low off.</x:v>
       </x:c>
       <x:c r="E69" s="1"/>
       <x:c r="F69" s="1"/>
@@ -12679,8 +12679,8 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f7559dc01174432"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6eeac784a8cc4dcd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R863eb9a905bb403c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b8d6492fb9f47c1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/samc21-pin-allocation/samc21_pin_allocation.xlsx
+++ b/outputs/samc21-pin-allocation/samc21_pin_allocation.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rd62105511ec04276"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAM0" sheetId="2" r:id="Ra95331f3afd04a8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAM1" sheetId="3" r:id="R2754fb636f6d4fbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAM2" sheetId="4" r:id="R01ad8cdfad4c4571"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STM32" sheetId="5" r:id="R706c7d5b7fd94946"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FTDI" sheetId="6" r:id="Rc5b64abebf824b07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R7b705d8d777044c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAM0" sheetId="2" r:id="R2046dd9779f44fc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAM1" sheetId="3" r:id="R02352bb31fad4b5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAM2" sheetId="4" r:id="R9f8be2595b494994"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STM32" sheetId="5" r:id="R6fee3dca5dbe4f27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FTDI" sheetId="6" r:id="R136492efd3ed4f9d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -505,7 +505,7 @@
         <x:v>Scope</x:v>
       </x:c>
       <x:c r="B4" s="3" t="str">
-        <x:v>264 pad rows: SAMs 3 × 48, STM32 64, FTDI 48 and EEPROM 8. All allocations remain unverified; no Board 1 CAD exists.</x:v>
+        <x:v>264 physical pad rows: SAMs 3 × 48, STM32 64, FTDI 48 and EEPROM 8. Native schematic in boards/board1/kicad. Evidence statuses remain unverified.</x:v>
       </x:c>
       <x:c r="C4" s="3" t="str">
         <x:v>B1-R001/005; B1-Q002/005/012; ADR-004/018</x:v>
@@ -582,7 +582,7 @@
         <x:v>Timing / LED</x:v>
       </x:c>
       <x:c r="B11" s="3" t="str">
-        <x:v>One LED per MCU; combined timing/debug headers per ADR-041. Timing pad assignment TBD.</x:v>
+        <x:v>GW: PC0 SYNC, PC1 TRIG, PC2/PC3 EVENT0/1. SAMs: PA02 SYNC, PA03 TRIG, PB08/PB09 EVENT0/1. One private LED per MCU.</x:v>
       </x:c>
       <x:c r="C11" s="3" t="str">
         <x:v>ADR-041; B1-R019/027</x:v>
@@ -626,10 +626,10 @@
         <x:v>Errata</x:v>
       </x:c>
       <x:c r="B15" s="3" t="str">
-        <x:v>DS80000740E identifies ATSAMC21G17A on p.2. Silicon revision is TBD; applicable CAN/USART/clock workarounds are not yet signed off.</x:v>
+        <x:v>DS80000740T (2026): clear initial EIC flags before enabling interrupts. Use synchronous EIC for standby edges. Record silicon revision and apply relevant CAN/USART/clock workarounds.</x:v>
       </x:c>
       <x:c r="C15" s="3" t="str">
-        <x:v>https://ww1.microchip.com/downloads/en/DeviceDoc/SAM-C20-C21-Family-Errata-DS80000740E.pdf</x:v>
+        <x:v>https://ww1.microchip.com/downloads/aemDocuments/documents/MCU32/ProductDocuments/Errata/SAM-C20-C21-Family-Silicon-Errata-and-Data-Sheet-Clarification-DS80000740.pdf</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="48" customHeight="1">
@@ -894,16 +894,16 @@
         <x:v>PA02</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
-        <x:v>TEST_IO_TBD</x:v>
+        <x:v>SYNC</x:v>
       </x:c>
       <x:c r="E7" s="9" t="str">
-        <x:v>TBD</x:v>
+        <x:v>EIC/EXTINT[2]</x:v>
       </x:c>
       <x:c r="F7" s="9" t="str">
-        <x:v>TBD</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="G7" s="3" t="str">
-        <x:v>TBD</x:v>
+        <x:v>In</x:v>
       </x:c>
       <x:c r="H7" s="3" t="str">
         <x:v>NA</x:v>
@@ -912,10 +912,10 @@
         <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J7" s="3" t="str">
-        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
+        <x:v>Header 4 shared SYNC through this MCU's 330 ohm branch. Global 10 kohm pull-down. Disable internal pulls.</x:v>
       </x:c>
       <x:c r="K7" s="3" t="str">
-        <x:v>DS60001479J p.22; 29</x:v>
+        <x:v>DS60001479J pp.22,29; Table 6-2</x:v>
       </x:c>
       <x:c r="L7" s="3" t="str">
         <x:v>https://ww1.microchip.com/downloads/en/DeviceDoc/SAM-C20-C21-Family-Data-Sheet-DS60001479J.pdf</x:v>
@@ -935,16 +935,16 @@
         <x:v>PA03</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>TEST_IO_TBD</x:v>
+        <x:v>TRIG</x:v>
       </x:c>
       <x:c r="E8" s="9" t="str">
-        <x:v>TBD</x:v>
+        <x:v>EIC/EXTINT[3]</x:v>
       </x:c>
       <x:c r="F8" s="9" t="str">
-        <x:v>TBD</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="G8" s="3" t="str">
-        <x:v>TBD</x:v>
+        <x:v>In</x:v>
       </x:c>
       <x:c r="H8" s="3" t="str">
         <x:v>NA</x:v>
@@ -953,10 +953,10 @@
         <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J8" s="3" t="str">
-        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
+        <x:v>Header 5 shared TRIG through this MCU's 330 ohm branch. Global 10 kohm pull-down. Disable internal pulls.</x:v>
       </x:c>
       <x:c r="K8" s="3" t="str">
-        <x:v>DS60001479J p.22; 29</x:v>
+        <x:v>DS60001479J pp.22,29; Table 6-2</x:v>
       </x:c>
       <x:c r="L8" s="3" t="str">
         <x:v>https://ww1.microchip.com/downloads/en/DeviceDoc/SAM-C20-C21-Family-Data-Sheet-DS60001479J.pdf</x:v>
@@ -1058,16 +1058,16 @@
         <x:v>PB08</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
-        <x:v>TEST_IO_TBD</x:v>
+        <x:v>EVENT0</x:v>
       </x:c>
       <x:c r="E11" s="9" t="str">
-        <x:v>TBD</x:v>
+        <x:v>PORT</x:v>
       </x:c>
       <x:c r="F11" s="9" t="str">
-        <x:v>TBD</x:v>
+        <x:v>GPIO</x:v>
       </x:c>
       <x:c r="G11" s="3" t="str">
-        <x:v>TBD</x:v>
+        <x:v>Out</x:v>
       </x:c>
       <x:c r="H11" s="3" t="str">
         <x:v>NA</x:v>
@@ -1076,10 +1076,10 @@
         <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J11" s="3" t="str">
-        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
+        <x:v>Header 7: private SAM0_EVENT0 output through 330 ohm near MCU. High-impedance measurement load.</x:v>
       </x:c>
       <x:c r="K11" s="3" t="str">
-        <x:v>DS60001479J p.22; 29</x:v>
+        <x:v>DS60001479J pp.22,29; Table 6-2</x:v>
       </x:c>
       <x:c r="L11" s="3" t="str">
         <x:v>https://ww1.microchip.com/downloads/en/DeviceDoc/SAM-C20-C21-Family-Data-Sheet-DS60001479J.pdf</x:v>
@@ -1099,16 +1099,16 @@
         <x:v>PB09</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>TEST_IO_TBD</x:v>
+        <x:v>EVENT1</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
-        <x:v>TBD</x:v>
+        <x:v>PORT</x:v>
       </x:c>
       <x:c r="F12" s="9" t="str">
-        <x:v>TBD</x:v>
+        <x:v>GPIO</x:v>
       </x:c>
       <x:c r="G12" s="3" t="str">
-        <x:v>TBD</x:v>
+        <x:v>Out</x:v>
       </x:c>
       <x:c r="H12" s="3" t="str">
         <x:v>NA</x:v>
@@ -1117,10 +1117,10 @@
         <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J12" s="3" t="str">
-        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
+        <x:v>Header 8: private SAM0_EVENT1 output through 330 ohm near MCU. High-impedance measurement load.</x:v>
       </x:c>
       <x:c r="K12" s="3" t="str">
-        <x:v>DS60001479J p.22; 29</x:v>
+        <x:v>DS60001479J pp.22,29; Table 6-2</x:v>
       </x:c>
       <x:c r="L12" s="3" t="str">
         <x:v>https://ww1.microchip.com/downloads/en/DeviceDoc/SAM-C20-C21-Family-Data-Sheet-DS60001479J.pdf</x:v>
@@ -2429,7 +2429,7 @@
         <x:v>B1-R007</x:v>
       </x:c>
       <x:c r="J44" s="3" t="str">
-        <x:v>To individual SWD header nRESET. Pull/RC and probe behavior TBD.</x:v>
+        <x:v>Individual SWD nRESET, 10 kohm pull-up and 10 nF to GND. No reset button.</x:v>
       </x:c>
       <x:c r="K44" s="3" t="str">
         <x:v>DS60001479J p.22</x:v>
@@ -2634,10 +2634,10 @@
         <x:v>B1-R007</x:v>
       </x:c>
       <x:c r="J49" s="3" t="str">
-        <x:v>Individual SWD header. Preserve debug ownership; no GPIO breakout.</x:v>
+        <x:v>Individual SWD SWCLK with 10 kohm pull-up. Table 53-7 permits 10–50 kohm. Preserve debug ownership.</x:v>
       </x:c>
       <x:c r="K49" s="3" t="str">
-        <x:v>DS60001479J p.22; 34</x:v>
+        <x:v>DS60001479J pp.22,34,1182; Table 53-7</x:v>
       </x:c>
       <x:c r="L49" s="3" t="str">
         <x:v>https://ww1.microchip.com/downloads/en/DeviceDoc/SAM-C20-C21-Family-Data-Sheet-DS60001479J.pdf</x:v>
@@ -2776,7 +2776,7 @@
       <x:c r="B55" s="1"/>
       <x:c r="C55" s="1"/>
       <x:c r="D55" s="1" t="str">
-        <x:v>ADR-041: one 1x8 timing/debug header per MCU. RX, TX, GND, SYNC, TRIG, GND, EVENT0, EVENT1. Timing MCU pads TBD; debug UART mapping retained.</x:v>
+        <x:v>Timing: PA02=SYNC/EXTINT2, PA03=TRIG/EXTINT3, PB08=EVENT0, PB09=EVENT1. Header RX, TX, GND, SYNC, TRIG, GND, EVENT0, EVENT1.</x:v>
       </x:c>
       <x:c r="E55" s="1"/>
       <x:c r="F55" s="1"/>
@@ -2799,7 +2799,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f726f3bc1c54f39"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ce4df3c864548be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3006,16 +3006,16 @@
         <x:v>PA02</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
-        <x:v>TEST_IO_TBD</x:v>
+        <x:v>SYNC</x:v>
       </x:c>
       <x:c r="E7" s="9" t="str">
-        <x:v>TBD</x:v>
+        <x:v>EIC/EXTINT[2]</x:v>
       </x:c>
       <x:c r="F7" s="9" t="str">
-        <x:v>TBD</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="G7" s="3" t="str">
-        <x:v>TBD</x:v>
+        <x:v>In</x:v>
       </x:c>
       <x:c r="H7" s="3" t="str">
         <x:v>NA</x:v>
@@ -3024,10 +3024,10 @@
         <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J7" s="3" t="str">
-        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
+        <x:v>Header 4 shared SYNC through this MCU's 330 ohm branch. Global 10 kohm pull-down. Disable internal pulls.</x:v>
       </x:c>
       <x:c r="K7" s="3" t="str">
-        <x:v>DS60001479J p.22; 29</x:v>
+        <x:v>DS60001479J pp.22,29; Table 6-2</x:v>
       </x:c>
       <x:c r="L7" s="3" t="str">
         <x:v>https://ww1.microchip.com/downloads/en/DeviceDoc/SAM-C20-C21-Family-Data-Sheet-DS60001479J.pdf</x:v>
@@ -3047,16 +3047,16 @@
         <x:v>PA03</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>TEST_IO_TBD</x:v>
+        <x:v>TRIG</x:v>
       </x:c>
       <x:c r="E8" s="9" t="str">
-        <x:v>TBD</x:v>
+        <x:v>EIC/EXTINT[3]</x:v>
       </x:c>
       <x:c r="F8" s="9" t="str">
-        <x:v>TBD</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="G8" s="3" t="str">
-        <x:v>TBD</x:v>
+        <x:v>In</x:v>
       </x:c>
       <x:c r="H8" s="3" t="str">
         <x:v>NA</x:v>
@@ -3065,10 +3065,10 @@
         <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J8" s="3" t="str">
-        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
+        <x:v>Header 5 shared TRIG through this MCU's 330 ohm branch. Global 10 kohm pull-down. Disable internal pulls.</x:v>
       </x:c>
       <x:c r="K8" s="3" t="str">
-        <x:v>DS60001479J p.22; 29</x:v>
+        <x:v>DS60001479J pp.22,29; Table 6-2</x:v>
       </x:c>
       <x:c r="L8" s="3" t="str">
         <x:v>https://ww1.microchip.com/downloads/en/DeviceDoc/SAM-C20-C21-Family-Data-Sheet-DS60001479J.pdf</x:v>
@@ -3170,16 +3170,16 @@
         <x:v>PB08</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
-        <x:v>TEST_IO_TBD</x:v>
+        <x:v>EVENT0</x:v>
       </x:c>
       <x:c r="E11" s="9" t="str">
-        <x:v>TBD</x:v>
+        <x:v>PORT</x:v>
       </x:c>
       <x:c r="F11" s="9" t="str">
-        <x:v>TBD</x:v>
+        <x:v>GPIO</x:v>
       </x:c>
       <x:c r="G11" s="3" t="str">
-        <x:v>TBD</x:v>
+        <x:v>Out</x:v>
       </x:c>
       <x:c r="H11" s="3" t="str">
         <x:v>NA</x:v>
@@ -3188,10 +3188,10 @@
         <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J11" s="3" t="str">
-        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
+        <x:v>Header 7: private SAM1_EVENT0 output through 330 ohm near MCU. High-impedance measurement load.</x:v>
       </x:c>
       <x:c r="K11" s="3" t="str">
-        <x:v>DS60001479J p.22; 29</x:v>
+        <x:v>DS60001479J pp.22,29; Table 6-2</x:v>
       </x:c>
       <x:c r="L11" s="3" t="str">
         <x:v>https://ww1.microchip.com/downloads/en/DeviceDoc/SAM-C20-C21-Family-Data-Sheet-DS60001479J.pdf</x:v>
@@ -3211,16 +3211,16 @@
         <x:v>PB09</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>TEST_IO_TBD</x:v>
+        <x:v>EVENT1</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
-        <x:v>TBD</x:v>
+        <x:v>PORT</x:v>
       </x:c>
       <x:c r="F12" s="9" t="str">
-        <x:v>TBD</x:v>
+        <x:v>GPIO</x:v>
       </x:c>
       <x:c r="G12" s="3" t="str">
-        <x:v>TBD</x:v>
+        <x:v>Out</x:v>
       </x:c>
       <x:c r="H12" s="3" t="str">
         <x:v>NA</x:v>
@@ -3229,10 +3229,10 @@
         <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J12" s="3" t="str">
-        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
+        <x:v>Header 8: private SAM1_EVENT1 output through 330 ohm near MCU. High-impedance measurement load.</x:v>
       </x:c>
       <x:c r="K12" s="3" t="str">
-        <x:v>DS60001479J p.22; 29</x:v>
+        <x:v>DS60001479J pp.22,29; Table 6-2</x:v>
       </x:c>
       <x:c r="L12" s="3" t="str">
         <x:v>https://ww1.microchip.com/downloads/en/DeviceDoc/SAM-C20-C21-Family-Data-Sheet-DS60001479J.pdf</x:v>
@@ -4541,7 +4541,7 @@
         <x:v>B1-R007</x:v>
       </x:c>
       <x:c r="J44" s="3" t="str">
-        <x:v>To individual SWD header nRESET. Pull/RC and probe behavior TBD.</x:v>
+        <x:v>Individual SWD nRESET, 10 kohm pull-up and 10 nF to GND. No reset button.</x:v>
       </x:c>
       <x:c r="K44" s="3" t="str">
         <x:v>DS60001479J p.22</x:v>
@@ -4746,10 +4746,10 @@
         <x:v>B1-R007</x:v>
       </x:c>
       <x:c r="J49" s="3" t="str">
-        <x:v>Individual SWD header. Preserve debug ownership; no GPIO breakout.</x:v>
+        <x:v>Individual SWD SWCLK with 10 kohm pull-up. Table 53-7 permits 10–50 kohm. Preserve debug ownership.</x:v>
       </x:c>
       <x:c r="K49" s="3" t="str">
-        <x:v>DS60001479J p.22; 34</x:v>
+        <x:v>DS60001479J pp.22,34,1182; Table 53-7</x:v>
       </x:c>
       <x:c r="L49" s="3" t="str">
         <x:v>https://ww1.microchip.com/downloads/en/DeviceDoc/SAM-C20-C21-Family-Data-Sheet-DS60001479J.pdf</x:v>
@@ -4888,7 +4888,7 @@
       <x:c r="B55" s="1"/>
       <x:c r="C55" s="1"/>
       <x:c r="D55" s="1" t="str">
-        <x:v>ADR-041: one 1x8 timing/debug header per MCU. RX, TX, GND, SYNC, TRIG, GND, EVENT0, EVENT1. Timing MCU pads TBD; debug UART mapping retained.</x:v>
+        <x:v>Timing: PA02=SYNC/EXTINT2, PA03=TRIG/EXTINT3, PB08=EVENT0, PB09=EVENT1. Header RX, TX, GND, SYNC, TRIG, GND, EVENT0, EVENT1.</x:v>
       </x:c>
       <x:c r="E55" s="1"/>
       <x:c r="F55" s="1"/>
@@ -4911,7 +4911,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8affdae8a57a4e1a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a5ca7edaecc4136"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5118,16 +5118,16 @@
         <x:v>PA02</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
-        <x:v>TEST_IO_TBD</x:v>
+        <x:v>SYNC</x:v>
       </x:c>
       <x:c r="E7" s="9" t="str">
-        <x:v>TBD</x:v>
+        <x:v>EIC/EXTINT[2]</x:v>
       </x:c>
       <x:c r="F7" s="9" t="str">
-        <x:v>TBD</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="G7" s="3" t="str">
-        <x:v>TBD</x:v>
+        <x:v>In</x:v>
       </x:c>
       <x:c r="H7" s="3" t="str">
         <x:v>NA</x:v>
@@ -5136,10 +5136,10 @@
         <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J7" s="3" t="str">
-        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
+        <x:v>Header 4 shared SYNC through this MCU's 330 ohm branch. Global 10 kohm pull-down. Disable internal pulls.</x:v>
       </x:c>
       <x:c r="K7" s="3" t="str">
-        <x:v>DS60001479J p.22; 29</x:v>
+        <x:v>DS60001479J pp.22,29; Table 6-2</x:v>
       </x:c>
       <x:c r="L7" s="3" t="str">
         <x:v>https://ww1.microchip.com/downloads/en/DeviceDoc/SAM-C20-C21-Family-Data-Sheet-DS60001479J.pdf</x:v>
@@ -5159,16 +5159,16 @@
         <x:v>PA03</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>TEST_IO_TBD</x:v>
+        <x:v>TRIG</x:v>
       </x:c>
       <x:c r="E8" s="9" t="str">
-        <x:v>TBD</x:v>
+        <x:v>EIC/EXTINT[3]</x:v>
       </x:c>
       <x:c r="F8" s="9" t="str">
-        <x:v>TBD</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="G8" s="3" t="str">
-        <x:v>TBD</x:v>
+        <x:v>In</x:v>
       </x:c>
       <x:c r="H8" s="3" t="str">
         <x:v>NA</x:v>
@@ -5177,10 +5177,10 @@
         <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J8" s="3" t="str">
-        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
+        <x:v>Header 5 shared TRIG through this MCU's 330 ohm branch. Global 10 kohm pull-down. Disable internal pulls.</x:v>
       </x:c>
       <x:c r="K8" s="3" t="str">
-        <x:v>DS60001479J p.22; 29</x:v>
+        <x:v>DS60001479J pp.22,29; Table 6-2</x:v>
       </x:c>
       <x:c r="L8" s="3" t="str">
         <x:v>https://ww1.microchip.com/downloads/en/DeviceDoc/SAM-C20-C21-Family-Data-Sheet-DS60001479J.pdf</x:v>
@@ -5282,16 +5282,16 @@
         <x:v>PB08</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
-        <x:v>TEST_IO_TBD</x:v>
+        <x:v>EVENT0</x:v>
       </x:c>
       <x:c r="E11" s="9" t="str">
-        <x:v>TBD</x:v>
+        <x:v>PORT</x:v>
       </x:c>
       <x:c r="F11" s="9" t="str">
-        <x:v>TBD</x:v>
+        <x:v>GPIO</x:v>
       </x:c>
       <x:c r="G11" s="3" t="str">
-        <x:v>TBD</x:v>
+        <x:v>Out</x:v>
       </x:c>
       <x:c r="H11" s="3" t="str">
         <x:v>NA</x:v>
@@ -5300,10 +5300,10 @@
         <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J11" s="3" t="str">
-        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
+        <x:v>Header 7: private SAM2_EVENT0 output through 330 ohm near MCU. High-impedance measurement load.</x:v>
       </x:c>
       <x:c r="K11" s="3" t="str">
-        <x:v>DS60001479J p.22; 29</x:v>
+        <x:v>DS60001479J pp.22,29; Table 6-2</x:v>
       </x:c>
       <x:c r="L11" s="3" t="str">
         <x:v>https://ww1.microchip.com/downloads/en/DeviceDoc/SAM-C20-C21-Family-Data-Sheet-DS60001479J.pdf</x:v>
@@ -5323,16 +5323,16 @@
         <x:v>PB09</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>TEST_IO_TBD</x:v>
+        <x:v>EVENT1</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
-        <x:v>TBD</x:v>
+        <x:v>PORT</x:v>
       </x:c>
       <x:c r="F12" s="9" t="str">
-        <x:v>TBD</x:v>
+        <x:v>GPIO</x:v>
       </x:c>
       <x:c r="G12" s="3" t="str">
-        <x:v>TBD</x:v>
+        <x:v>Out</x:v>
       </x:c>
       <x:c r="H12" s="3" t="str">
         <x:v>NA</x:v>
@@ -5341,10 +5341,10 @@
         <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J12" s="3" t="str">
-        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
+        <x:v>Header 8: private SAM2_EVENT1 output through 330 ohm near MCU. High-impedance measurement load.</x:v>
       </x:c>
       <x:c r="K12" s="3" t="str">
-        <x:v>DS60001479J p.22; 29</x:v>
+        <x:v>DS60001479J pp.22,29; Table 6-2</x:v>
       </x:c>
       <x:c r="L12" s="3" t="str">
         <x:v>https://ww1.microchip.com/downloads/en/DeviceDoc/SAM-C20-C21-Family-Data-Sheet-DS60001479J.pdf</x:v>
@@ -6653,7 +6653,7 @@
         <x:v>B1-R007</x:v>
       </x:c>
       <x:c r="J44" s="3" t="str">
-        <x:v>To individual SWD header nRESET. Pull/RC and probe behavior TBD.</x:v>
+        <x:v>Individual SWD nRESET, 10 kohm pull-up and 10 nF to GND. No reset button.</x:v>
       </x:c>
       <x:c r="K44" s="3" t="str">
         <x:v>DS60001479J p.22</x:v>
@@ -6858,10 +6858,10 @@
         <x:v>B1-R007</x:v>
       </x:c>
       <x:c r="J49" s="3" t="str">
-        <x:v>Individual SWD header. Preserve debug ownership; no GPIO breakout.</x:v>
+        <x:v>Individual SWD SWCLK with 10 kohm pull-up. Table 53-7 permits 10–50 kohm. Preserve debug ownership.</x:v>
       </x:c>
       <x:c r="K49" s="3" t="str">
-        <x:v>DS60001479J p.22; 34</x:v>
+        <x:v>DS60001479J pp.22,34,1182; Table 53-7</x:v>
       </x:c>
       <x:c r="L49" s="3" t="str">
         <x:v>https://ww1.microchip.com/downloads/en/DeviceDoc/SAM-C20-C21-Family-Data-Sheet-DS60001479J.pdf</x:v>
@@ -7000,7 +7000,7 @@
       <x:c r="B55" s="1"/>
       <x:c r="C55" s="1"/>
       <x:c r="D55" s="1" t="str">
-        <x:v>ADR-041: one 1x8 timing/debug header per MCU. RX, TX, GND, SYNC, TRIG, GND, EVENT0, EVENT1. Timing MCU pads TBD; debug UART mapping retained.</x:v>
+        <x:v>Timing: PA02=SYNC/EXTINT2, PA03=TRIG/EXTINT3, PB08=EVENT0, PB09=EVENT1. Header RX, TX, GND, SYNC, TRIG, GND, EVENT0, EVENT1.</x:v>
       </x:c>
       <x:c r="E55" s="1"/>
       <x:c r="F55" s="1"/>
@@ -7023,7 +7023,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fcd677ece3c4e87"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20d4e95d93374207"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7412,7 +7412,7 @@
         <x:v>B1-R007</x:v>
       </x:c>
       <x:c r="J11" s="3" t="str">
-        <x:v>Independent SWD nRESET. Preserve NRST reset function and default released. No CBUS connection in Rev A (ADR-042); B1-Q005.</x:v>
+        <x:v>Individual SWD nRESET, 10 kohm pull-up and 100 nF to GND. Preserve NRST mode. No CBUS circuit (ADR-042).</x:v>
       </x:c>
       <x:c r="K11" s="3" t="str">
         <x:v>DS12288 Rev.6 p.50; 58; 72</x:v>
@@ -7435,16 +7435,16 @@
         <x:v>PC0</x:v>
       </x:c>
       <x:c r="D12" s="13" t="str">
-        <x:v>TEST_IO_TBD</x:v>
+        <x:v>SYNC</x:v>
       </x:c>
       <x:c r="E12" s="13" t="str">
-        <x:v>TBD</x:v>
+        <x:v>EXTI0</x:v>
       </x:c>
       <x:c r="F12" s="13" t="str">
-        <x:v>TBD</x:v>
+        <x:v>GPIO/SYSCFG port C</x:v>
       </x:c>
       <x:c r="G12" s="3" t="str">
-        <x:v>TBD</x:v>
+        <x:v>In</x:v>
       </x:c>
       <x:c r="H12" s="3" t="str">
         <x:v>NA</x:v>
@@ -7453,10 +7453,10 @@
         <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J12" s="3" t="str">
-        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
+        <x:v>Header 4 shared SYNC through this MCU's 330 ohm branch. Global 10 kohm pull-down. Disable internal pulls.</x:v>
       </x:c>
       <x:c r="K12" s="3" t="str">
-        <x:v>DS12288 Rev.6 p.50; 58–59; 75</x:v>
+        <x:v>DS12288 Rev.6 pp.50,59; RM0440 SYSCFG_EXTICR1</x:v>
       </x:c>
       <x:c r="L12" s="3" t="str">
         <x:v>https://www.st.com/resource/en/datasheet/stm32g474rb.pdf</x:v>
@@ -7476,16 +7476,16 @@
         <x:v>PC1</x:v>
       </x:c>
       <x:c r="D13" s="13" t="str">
-        <x:v>TEST_IO_TBD</x:v>
+        <x:v>TRIG</x:v>
       </x:c>
       <x:c r="E13" s="13" t="str">
-        <x:v>TBD</x:v>
+        <x:v>EXTI1</x:v>
       </x:c>
       <x:c r="F13" s="13" t="str">
-        <x:v>TBD</x:v>
+        <x:v>GPIO/SYSCFG port C</x:v>
       </x:c>
       <x:c r="G13" s="3" t="str">
-        <x:v>TBD</x:v>
+        <x:v>In</x:v>
       </x:c>
       <x:c r="H13" s="3" t="str">
         <x:v>NA</x:v>
@@ -7494,10 +7494,10 @@
         <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J13" s="3" t="str">
-        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
+        <x:v>Header 5 shared TRIG through this MCU's 330 ohm branch. Global 10 kohm pull-down. Disable internal pulls.</x:v>
       </x:c>
       <x:c r="K13" s="3" t="str">
-        <x:v>DS12288 Rev.6 p.50; 58–59; 75</x:v>
+        <x:v>DS12288 Rev.6 pp.50,59; RM0440 SYSCFG_EXTICR1</x:v>
       </x:c>
       <x:c r="L13" s="3" t="str">
         <x:v>https://www.st.com/resource/en/datasheet/stm32g474rb.pdf</x:v>
@@ -7517,16 +7517,16 @@
         <x:v>PC2</x:v>
       </x:c>
       <x:c r="D14" s="13" t="str">
-        <x:v>TEST_IO_TBD</x:v>
+        <x:v>EVENT0</x:v>
       </x:c>
       <x:c r="E14" s="13" t="str">
-        <x:v>TBD</x:v>
+        <x:v>GPIO</x:v>
       </x:c>
       <x:c r="F14" s="13" t="str">
-        <x:v>TBD</x:v>
+        <x:v>GPIO</x:v>
       </x:c>
       <x:c r="G14" s="3" t="str">
-        <x:v>TBD</x:v>
+        <x:v>Out</x:v>
       </x:c>
       <x:c r="H14" s="3" t="str">
         <x:v>NA</x:v>
@@ -7535,10 +7535,10 @@
         <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J14" s="3" t="str">
-        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
+        <x:v>Header 7: private GW_EVENT0 output through 330 ohm near MCU. High-impedance measurement load.</x:v>
       </x:c>
       <x:c r="K14" s="3" t="str">
-        <x:v>DS12288 Rev.6 p.50; 58–59; 75</x:v>
+        <x:v>DS12288 Rev.6 pp.50,59; RM0440 SYSCFG_EXTICR1</x:v>
       </x:c>
       <x:c r="L14" s="3" t="str">
         <x:v>https://www.st.com/resource/en/datasheet/stm32g474rb.pdf</x:v>
@@ -7558,16 +7558,16 @@
         <x:v>PC3</x:v>
       </x:c>
       <x:c r="D15" s="13" t="str">
-        <x:v>TEST_IO_TBD</x:v>
+        <x:v>EVENT1</x:v>
       </x:c>
       <x:c r="E15" s="13" t="str">
-        <x:v>TBD</x:v>
+        <x:v>GPIO</x:v>
       </x:c>
       <x:c r="F15" s="13" t="str">
-        <x:v>TBD</x:v>
+        <x:v>GPIO</x:v>
       </x:c>
       <x:c r="G15" s="3" t="str">
-        <x:v>TBD</x:v>
+        <x:v>Out</x:v>
       </x:c>
       <x:c r="H15" s="3" t="str">
         <x:v>NA</x:v>
@@ -7576,10 +7576,10 @@
         <x:v>B1-R027</x:v>
       </x:c>
       <x:c r="J15" s="3" t="str">
-        <x:v>Timing pad TBD (B1-Q005/010). SYNC/TRIG global inputs; EVENT0/1 private outputs. Each needs 330 ohm near MCU, ADR-042.</x:v>
+        <x:v>Header 8: private GW_EVENT1 output through 330 ohm near MCU. High-impedance measurement load.</x:v>
       </x:c>
       <x:c r="K15" s="3" t="str">
-        <x:v>DS12288 Rev.6 p.50; 58–59; 75</x:v>
+        <x:v>DS12288 Rev.6 pp.50,59; RM0440 SYSCFG_EXTICR1</x:v>
       </x:c>
       <x:c r="L15" s="3" t="str">
         <x:v>https://www.st.com/resource/en/datasheet/stm32g474rb.pdf</x:v>
@@ -7883,31 +7883,31 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C23" s="3" t="str">
-        <x:v>VSSA</x:v>
+        <x:v>PA5</x:v>
       </x:c>
       <x:c r="D23" s="13" t="str">
-        <x:v>GND</x:v>
+        <x:v>LED</x:v>
       </x:c>
       <x:c r="E23" s="13" t="str">
-        <x:v>Power</x:v>
+        <x:v>GPIO</x:v>
       </x:c>
       <x:c r="F23" s="13" t="str">
-        <x:v>NA</x:v>
+        <x:v>GPIO</x:v>
       </x:c>
       <x:c r="G23" s="3" t="str">
-        <x:v>Ground</x:v>
+        <x:v>Out</x:v>
       </x:c>
       <x:c r="H23" s="3" t="str">
-        <x:v>B1-P006</x:v>
+        <x:v>NA</x:v>
       </x:c>
       <x:c r="I23" s="3" t="str">
-        <x:v>B1-R001</x:v>
+        <x:v>B1-R019</x:v>
       </x:c>
       <x:c r="J23" s="3" t="str">
-        <x:v>Connect ground. Local bypass returns and analog grounding require layout review.</x:v>
+        <x:v>PA5 pad 19 drives the MCU LED through 3.3 kohm. B1-B024/026, ADR-029/039.</x:v>
       </x:c>
       <x:c r="K23" s="3" t="str">
-        <x:v>DS12288 Rev.6 p.50; Table 12</x:v>
+        <x:v>DS12288 Rev.6 Table 12 pp.60–61; LQFP64</x:v>
       </x:c>
       <x:c r="L23" s="3" t="str">
         <x:v>https://www.st.com/resource/en/datasheet/stm32g474rb.pdf</x:v>
@@ -7924,19 +7924,19 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C24" s="3" t="str">
-        <x:v>VREF+</x:v>
+        <x:v>PA6</x:v>
       </x:c>
       <x:c r="D24" s="13" t="str">
-        <x:v>3V3_SYS</x:v>
+        <x:v>UNUSED</x:v>
       </x:c>
       <x:c r="E24" s="13" t="str">
-        <x:v>Power</x:v>
+        <x:v>NA</x:v>
       </x:c>
       <x:c r="F24" s="13" t="str">
         <x:v>NA</x:v>
       </x:c>
       <x:c r="G24" s="3" t="str">
-        <x:v>Supply in</x:v>
+        <x:v>NA</x:v>
       </x:c>
       <x:c r="H24" s="3" t="str">
         <x:v>B1-P006</x:v>
@@ -7945,10 +7945,10 @@
         <x:v>B1-R001</x:v>
       </x:c>
       <x:c r="J24" s="3" t="str">
-        <x:v>Shared VDDA/VREF+ supply per ADR-010. Keep VREFBUF disabled/high impedance when externally driven.</x:v>
+        <x:v>No connection or future circuitry reserved. Review firmware state.</x:v>
       </x:c>
       <x:c r="K24" s="3" t="str">
-        <x:v>DS12288 Rev.6 p.50; §3.11; Table 12</x:v>
+        <x:v>DS12288 Rev.6 Table 12 pp.60–61; LQFP64</x:v>
       </x:c>
       <x:c r="L24" s="3" t="str">
         <x:v>https://www.st.com/resource/en/datasheet/stm32g474rb.pdf</x:v>
@@ -7965,19 +7965,19 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C25" s="3" t="str">
-        <x:v>VDDA</x:v>
+        <x:v>PA7</x:v>
       </x:c>
       <x:c r="D25" s="13" t="str">
-        <x:v>3V3_SYS</x:v>
+        <x:v>UNUSED</x:v>
       </x:c>
       <x:c r="E25" s="13" t="str">
-        <x:v>Power</x:v>
+        <x:v>NA</x:v>
       </x:c>
       <x:c r="F25" s="13" t="str">
         <x:v>NA</x:v>
       </x:c>
       <x:c r="G25" s="3" t="str">
-        <x:v>Supply in</x:v>
+        <x:v>NA</x:v>
       </x:c>
       <x:c r="H25" s="3" t="str">
         <x:v>B1-P006</x:v>
@@ -7986,10 +7986,10 @@
         <x:v>B1-R001</x:v>
       </x:c>
       <x:c r="J25" s="3" t="str">
-        <x:v>Local bypass/bulk per ADR-010. This LQFP64 has no external VCAP pin.</x:v>
+        <x:v>No connection or future circuitry reserved. Review firmware state.</x:v>
       </x:c>
       <x:c r="K25" s="3" t="str">
-        <x:v>DS12288 Rev.6 p.50; §3.11; Table 12</x:v>
+        <x:v>DS12288 Rev.6 Table 12 pp.60–61; LQFP64</x:v>
       </x:c>
       <x:c r="L25" s="3" t="str">
         <x:v>https://www.st.com/resource/en/datasheet/stm32g474rb.pdf</x:v>
@@ -8006,31 +8006,31 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="C26" s="3" t="str">
-        <x:v>PA5</x:v>
+        <x:v>PC4</x:v>
       </x:c>
       <x:c r="D26" s="13" t="str">
-        <x:v>LED</x:v>
+        <x:v>UNUSED</x:v>
       </x:c>
       <x:c r="E26" s="13" t="str">
-        <x:v>GPIO</x:v>
+        <x:v>NA</x:v>
       </x:c>
       <x:c r="F26" s="13" t="str">
-        <x:v>GPIO</x:v>
+        <x:v>NA</x:v>
       </x:c>
       <x:c r="G26" s="3" t="str">
-        <x:v>Out</x:v>
+        <x:v>NA</x:v>
       </x:c>
       <x:c r="H26" s="3" t="str">
-        <x:v>NA</x:v>
+        <x:v>B1-P006</x:v>
       </x:c>
       <x:c r="I26" s="3" t="str">
-        <x:v>B1-R019</x:v>
+        <x:v>B1-R001</x:v>
       </x:c>
       <x:c r="J26" s="3" t="str">
-        <x:v>PA5 LED drive remains proposed. LED and resistor B1-B024/026 accepted ADR-029/039; current/visibility remain B1-Q010.</x:v>
+        <x:v>No connection or future circuitry reserved. Review firmware state.</x:v>
       </x:c>
       <x:c r="K26" s="3" t="str">
-        <x:v>DS12288 Rev.6 p.50; 60</x:v>
+        <x:v>DS12288 Rev.6 Table 12 pp.60–61; LQFP64</x:v>
       </x:c>
       <x:c r="L26" s="3" t="str">
         <x:v>https://www.st.com/resource/en/datasheet/stm32g474rb.pdf</x:v>
@@ -8047,7 +8047,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C27" s="3" t="str">
-        <x:v>PA6</x:v>
+        <x:v>PC5</x:v>
       </x:c>
       <x:c r="D27" s="13" t="str">
         <x:v>UNUSED</x:v>
@@ -8071,7 +8071,7 @@
         <x:v>No connection or future circuitry reserved. Review firmware state.</x:v>
       </x:c>
       <x:c r="K27" s="3" t="str">
-        <x:v>DS12288 Rev.6 p.50; Table 12</x:v>
+        <x:v>DS12288 Rev.6 Table 12 pp.60–61; LQFP64</x:v>
       </x:c>
       <x:c r="L27" s="3" t="str">
         <x:v>https://www.st.com/resource/en/datasheet/stm32g474rb.pdf</x:v>
@@ -8088,7 +8088,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="C28" s="3" t="str">
-        <x:v>PA7</x:v>
+        <x:v>PB0</x:v>
       </x:c>
       <x:c r="D28" s="13" t="str">
         <x:v>UNUSED</x:v>
@@ -8112,7 +8112,7 @@
         <x:v>No connection or future circuitry reserved. Review firmware state.</x:v>
       </x:c>
       <x:c r="K28" s="3" t="str">
-        <x:v>DS12288 Rev.6 p.50; Table 12</x:v>
+        <x:v>DS12288 Rev.6 Table 12 pp.60–61; LQFP64</x:v>
       </x:c>
       <x:c r="L28" s="3" t="str">
         <x:v>https://www.st.com/resource/en/datasheet/stm32g474rb.pdf</x:v>
@@ -8129,7 +8129,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="C29" s="3" t="str">
-        <x:v>PC4</x:v>
+        <x:v>PB1</x:v>
       </x:c>
       <x:c r="D29" s="13" t="str">
         <x:v>UNUSED</x:v>
@@ -8153,7 +8153,7 @@
         <x:v>No connection or future circuitry reserved. Review firmware state.</x:v>
       </x:c>
       <x:c r="K29" s="3" t="str">
-        <x:v>DS12288 Rev.6 p.50; Table 12</x:v>
+        <x:v>DS12288 Rev.6 Table 12 pp.60–61; LQFP64</x:v>
       </x:c>
       <x:c r="L29" s="3" t="str">
         <x:v>https://www.st.com/resource/en/datasheet/stm32g474rb.pdf</x:v>
@@ -8170,7 +8170,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C30" s="3" t="str">
-        <x:v>PC5</x:v>
+        <x:v>PB2</x:v>
       </x:c>
       <x:c r="D30" s="13" t="str">
         <x:v>UNUSED</x:v>
@@ -8194,7 +8194,7 @@
         <x:v>No connection or future circuitry reserved. Review firmware state.</x:v>
       </x:c>
       <x:c r="K30" s="3" t="str">
-        <x:v>DS12288 Rev.6 p.50; Table 12</x:v>
+        <x:v>DS12288 Rev.6 Table 12 pp.60–61; LQFP64</x:v>
       </x:c>
       <x:c r="L30" s="3" t="str">
         <x:v>https://www.st.com/resource/en/datasheet/stm32g474rb.pdf</x:v>
@@ -8211,19 +8211,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C31" s="3" t="str">
-        <x:v>PB0</x:v>
+        <x:v>VSSA</x:v>
       </x:c>
       <x:c r="D31" s="13" t="str">
-        <x:v>UNUSED</x:v>
+        <x:v>GND</x:v>
       </x:c>
       <x:c r="E31" s="13" t="str">
-        <x:v>NA</x:v>
+        <x:v>Power</x:v>
       </x:c>
       <x:c r="F31" s="13" t="str">
         <x:v>NA</x:v>
       </x:c>
       <x:c r="G31" s="3" t="str">
-        <x:v>NA</x:v>
+        <x:v>Ground</x:v>
       </x:c>
       <x:c r="H31" s="3" t="str">
         <x:v>B1-P006</x:v>
@@ -8232,10 +8232,10 @@
         <x:v>B1-R001</x:v>
       </x:c>
       <x:c r="J31" s="3" t="str">
-        <x:v>No connection or future circuitry reserved. Review firmware state.</x:v>
+        <x:v>Connect ground. Local bypass returns and analog grounding require layout review.</x:v>
       </x:c>
       <x:c r="K31" s="3" t="str">
-        <x:v>DS12288 Rev.6 p.50; Table 12</x:v>
+        <x:v>DS12288 Rev.6 Table 12 pp.60–61; LQFP64</x:v>
       </x:c>
       <x:c r="L31" s="3" t="str">
         <x:v>https://www.st.com/resource/en/datasheet/stm32g474rb.pdf</x:v>
@@ -8252,19 +8252,19 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="C32" s="3" t="str">
-        <x:v>PB1</x:v>
+        <x:v>VREF+</x:v>
       </x:c>
       <x:c r="D32" s="13" t="str">
-        <x:v>UNUSED</x:v>
+        <x:v>3V3_SYS</x:v>
       </x:c>
       <x:c r="E32" s="13" t="str">
-        <x:v>NA</x:v>
+        <x:v>Power</x:v>
       </x:c>
       <x:c r="F32" s="13" t="str">
         <x:v>NA</x:v>
       </x:c>
       <x:c r="G32" s="3" t="str">
-        <x:v>NA</x:v>
+        <x:v>Supply in</x:v>
       </x:c>
       <x:c r="H32" s="3" t="str">
         <x:v>B1-P006</x:v>
@@ -8273,10 +8273,10 @@
         <x:v>B1-R001</x:v>
       </x:c>
       <x:c r="J32" s="3" t="str">
-        <x:v>No connection or future circuitry reserved. Review firmware state.</x:v>
+        <x:v>Shared VDDA/VREF+ supply per ADR-010. Keep VREFBUF disabled/high impedance when externally driven.</x:v>
       </x:c>
       <x:c r="K32" s="3" t="str">
-        <x:v>DS12288 Rev.6 p.50; Table 12</x:v>
+        <x:v>DS12288 Rev.6 Table 12 pp.60–61; LQFP64</x:v>
       </x:c>
       <x:c r="L32" s="3" t="str">
         <x:v>https://www.st.com/resource/en/datasheet/stm32g474rb.pdf</x:v>
@@ -8293,19 +8293,19 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C33" s="3" t="str">
-        <x:v>PB2</x:v>
+        <x:v>VDDA</x:v>
       </x:c>
       <x:c r="D33" s="13" t="str">
-        <x:v>UNUSED</x:v>
+        <x:v>3V3_SYS</x:v>
       </x:c>
       <x:c r="E33" s="13" t="str">
-        <x:v>NA</x:v>
+        <x:v>Power</x:v>
       </x:c>
       <x:c r="F33" s="13" t="str">
         <x:v>NA</x:v>
       </x:c>
       <x:c r="G33" s="3" t="str">
-        <x:v>NA</x:v>
+        <x:v>Supply in</x:v>
       </x:c>
       <x:c r="H33" s="3" t="str">
         <x:v>B1-P006</x:v>
@@ -8314,10 +8314,10 @@
         <x:v>B1-R001</x:v>
       </x:c>
       <x:c r="J33" s="3" t="str">
-        <x:v>No connection or future circuitry reserved. Review firmware state.</x:v>
+        <x:v>Local bypass/bulk per ADR-010. This LQFP64 has no external VCAP pin.</x:v>
       </x:c>
       <x:c r="K33" s="3" t="str">
-        <x:v>DS12288 Rev.6 p.50; Table 12</x:v>
+        <x:v>DS12288 Rev.6 Table 12 pp.60–61; LQFP64</x:v>
       </x:c>
       <x:c r="L33" s="3" t="str">
         <x:v>https://www.st.com/resource/en/datasheet/stm32g474rb.pdf</x:v>
@@ -9626,7 +9626,7 @@
         <x:v>B1-R001</x:v>
       </x:c>
       <x:c r="J65" s="3" t="str">
-        <x:v>Default BOOT0 low; ordinary boot support B1-B010. Verify normal-boot option bytes B1-Q005. No CBUS connection in Rev A (ADR-042).</x:v>
+        <x:v>PB8-BOOT0 has 10 kohm to GND. First programming uses SWD with bus peers disconnected. Check normal-boot option bytes. ADR-042.</x:v>
       </x:c>
       <x:c r="K65" s="3" t="str">
         <x:v>DS12288 Rev.6 p.50; 71; §3.7</x:v>
@@ -9806,7 +9806,7 @@
       <x:c r="B73" s="1"/>
       <x:c r="C73" s="1"/>
       <x:c r="D73" s="1" t="str">
-        <x:v>Keep NRST/SWD and BOOT0-low defaults (B1-B010). Automated CBUS reset/BOOT0 deferred to Rev B, ADR-042. Reset support/option bytes remain B1-Q005.</x:v>
+        <x:v>NRST has 10 kohm pull-up and 100 nF to GND. BOOT0 has 10 kohm pull-down. SWD reset access retained. No automated CBUS recovery (ADR-042).</x:v>
       </x:c>
       <x:c r="E73" s="1"/>
       <x:c r="F73" s="1"/>
@@ -9958,7 +9958,7 @@
       <x:c r="B83" s="1"/>
       <x:c r="C83" s="1"/>
       <x:c r="D83" s="1" t="str">
-        <x:v>ADR-041: one 1x8 timing/debug header per MCU. RX, TX, GND, SYNC, TRIG, GND, EVENT0, EVENT1. Timing MCU pads TBD; debug UART mapping retained.</x:v>
+        <x:v>Timing: PC0=SYNC/EXTI0, PC1=TRIG/EXTI1, PC2=EVENT0, PC3=EVENT1. Six 330 ohm branches per header (ADR-042).</x:v>
       </x:c>
       <x:c r="E83" s="1"/>
       <x:c r="F83" s="1"/>
@@ -9973,7 +9973,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R646175e736c04cb7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87315b96bd324fbd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12679,8 +12679,8 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R863eb9a905bb403c"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b8d6492fb9f47c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b5ff27a96574001"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6201b0354536422c"/>
   </x:tableParts>
 </x:worksheet>
 </file>